--- a/AAII_Financials/Quarterly/WBD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WBD_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="92">
   <si>
     <t>WBD</t>
   </si>
@@ -656,221 +656,233 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>10284000</v>
+      </c>
+      <c r="E8" s="3">
         <v>9979000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>10358000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>10700000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>11008000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9823000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9827000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3159000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3187000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3150000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3062000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2792000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2886000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2561000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2541000</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>5885000</v>
+      </c>
+      <c r="E9" s="3">
         <v>5118000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6608000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6589000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6954000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4718000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6123000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1232000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1065000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1527000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1054000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>969000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1089000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1002000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>804000</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4399000</v>
+      </c>
+      <c r="E10" s="3">
         <v>4861000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3750000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4111000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4054000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5105000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3704000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1927000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2122000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1623000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2008000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1823000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1797000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1559000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1737000</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -888,8 +900,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -935,8 +948,11 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,102 +998,111 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>102000</v>
+      </c>
+      <c r="E14" s="3">
         <v>462000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>185000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>222000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1198000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2430000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1535000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>9000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>5000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>15000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>8000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>18000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>150000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>70000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>122000</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2024000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1989000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1914000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2058000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2169000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2233000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2266000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>525000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>539000</v>
-      </c>
-      <c r="L15" s="3">
-        <v>341000</v>
       </c>
       <c r="M15" s="3">
         <v>341000</v>
       </c>
       <c r="N15" s="3">
+        <v>341000</v>
+      </c>
+      <c r="O15" s="3">
         <v>361000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>358000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>341000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>334000</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1092,102 +1117,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>10466000</v>
+      </c>
+      <c r="E17" s="3">
         <v>9860000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>11269000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>11257000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>12902000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12013000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13466000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2806000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2679000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2827000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2284000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2399000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2406000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2046000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1895000</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-182000</v>
+      </c>
+      <c r="E18" s="3">
         <v>119000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-911000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-557000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1894000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2190000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-3639000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>353000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>508000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>323000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>778000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>393000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>480000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>515000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>646000</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1205,243 +1237,259 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>71000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-77000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-110000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-89000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-106000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-94000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>476000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-171000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>69000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>99000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>67000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>109000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-25000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5379000</v>
+      </c>
+      <c r="E21" s="3">
         <v>5026000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5618000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>6018000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4270000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3878000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3649000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2323000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1642000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1952000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1991000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1564000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1785000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1594000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1613000</v>
       </c>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>574000</v>
+        <v>502000</v>
       </c>
       <c r="E22" s="3">
         <v>574000</v>
       </c>
       <c r="F22" s="3">
+        <v>574000</v>
+      </c>
+      <c r="G22" s="3">
         <v>571000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>558000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>555000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>511000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>153000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>154000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>159000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>157000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>163000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>173000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>171000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>172000</v>
       </c>
     </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-613000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-532000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1480000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1238000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2541000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2851000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-4244000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>676000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>183000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>233000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>720000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>297000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>416000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>319000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>456000</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-221000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-125000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-260000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-178000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-462000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-566000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-836000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>201000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>92000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>36000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>106000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>98000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>156000</v>
       </c>
     </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1487,102 +1535,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-392000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-407000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1220000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1060000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2079000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2285000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3408000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>475000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>91000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>197000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>718000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>191000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>318000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>330000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>300000</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-400000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-417000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1240000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1069000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2101000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2308000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3418000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>407000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>48000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>120000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>515000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>106000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>205000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>223000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1628,8 +1685,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1675,8 +1735,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1722,8 +1785,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1769,102 +1835,111 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="E32" s="3">
         <v>77000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>110000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>89000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>106000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>94000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-476000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>171000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-69000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-99000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-67000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-109000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>25000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-400000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-417000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1240000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1069000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2101000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2308000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3418000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>407000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>48000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>120000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>515000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>106000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>205000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>223000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1910,107 +1985,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-400000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-417000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1240000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1069000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2101000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2308000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3418000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>407000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>48000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>120000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>515000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>106000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>205000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>223000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2028,8 +2112,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2047,55 +2132,59 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3780000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2383000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3027000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2594000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3731000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2422000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2575000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4162000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3905000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3116000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2834000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2008000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2091000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1893000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1683000</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2141,55 +2230,61 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6047000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6312000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6770000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6833000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6380000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6669000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7049000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2426000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2446000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2462000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2657000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2476000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2537000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2444000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2473000</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2235,243 +2330,261 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4391000</v>
+      </c>
+      <c r="E45" s="3">
         <v>4136000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3976000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4300000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3888000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3581000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5825000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>585000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>913000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1078000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1237000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1381000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1502000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1141000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>561000</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>14218000</v>
+      </c>
+      <c r="E46" s="3">
         <v>12831000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>13773000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>13727000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>13999000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12672000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>15449000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7173000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7264000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6656000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6728000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5865000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6130000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5478000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4717000</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D47" s="3">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3">
+        <v>0</v>
+      </c>
+      <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>543000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>545000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>559000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>522000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>507000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>536000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>530000</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9031000</v>
+      </c>
+      <c r="E48" s="3">
         <v>5810000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5473000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5325000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8490000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8365000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8515000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1328000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1336000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1310000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1239000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1189000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1206000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1125000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1088000</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>94483000</v>
+      </c>
+      <c r="E49" s="3">
         <v>97055000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>100888000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>103370000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>106072000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>109482000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>113117000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>22611000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>23061000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>23429000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>23694000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>23765000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>24149000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>24194000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>24618000</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2517,8 +2630,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2564,55 +2680,61 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5025000</v>
+      </c>
+      <c r="E52" s="3">
         <v>8053000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8484000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8162000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5440000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5530000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5159000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2687000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2223000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2378000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2352000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2284000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2095000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2105000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2136000</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2658,55 +2780,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>122757000</v>
+      </c>
+      <c r="E54" s="3">
         <v>123749000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>128618000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>130584000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>134001000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>136049000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>142240000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>33799000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>34427000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>34318000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>34572000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>33625000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>34087000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>33438000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>33089000</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2724,8 +2852,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2743,290 +2872,309 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1260000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1329000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1689000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1123000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1454000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1534000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1397000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>521000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>412000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2361000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2174000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2128000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>397000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>403000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>367000</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1854000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1302000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3001000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3496000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>447000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1338000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1175000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>794000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>397000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>349000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>585000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>351000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>392000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>336000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>339000</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>12218000</v>
+      </c>
+      <c r="E59" s="3">
         <v>11957000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>12216000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>11761000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>13116000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>11804000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>11864000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2247000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2650000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>625000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>806000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>663000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2293000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2017000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1870000</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>15332000</v>
+      </c>
+      <c r="E60" s="3">
         <v>14588000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>16906000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>16380000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>15017000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>14676000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>14436000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3562000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3459000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3335000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3565000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3142000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3082000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2756000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2576000</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>42080000</v>
+      </c>
+      <c r="E61" s="3">
         <v>43498000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>44276000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>45434000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>48820000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>48799000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>51594000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>13605000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>14617000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>14436000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>14462000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>14675000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>15253000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>14981000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>14944000</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>18873000</v>
+      </c>
+      <c r="E62" s="3">
         <v>19521000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>20651000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>20928000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>21497000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>22494000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>23263000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3070000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2955000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3149000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3237000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3233000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3369000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3661000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3769000</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3072,8 +3220,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3119,8 +3270,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3166,55 +3320,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>77531000</v>
+      </c>
+      <c r="E66" s="3">
         <v>78975000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>83166000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>84088000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>86906000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>87532000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>90857000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>21830000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>22828000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>22707000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>23034000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>22810000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>23623000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>23351000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>23222000</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3232,8 +3392,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3279,8 +3440,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3326,8 +3490,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3373,8 +3540,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3420,55 +3590,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-928000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-526000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-105000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1133000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2205000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4306000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6614000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>10033000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9580000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9522000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9360000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8682000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8543000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>8278000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7980000</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3514,8 +3690,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3561,8 +3740,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3608,55 +3790,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>45226000</v>
+      </c>
+      <c r="E76" s="3">
         <v>44774000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>45452000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>46496000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>47095000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>48517000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>51383000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11969000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11599000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11611000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11538000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10815000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10464000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10087000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9867000</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3702,107 +3890,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-400000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-417000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1240000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1069000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2101000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2308000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3418000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>407000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>48000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>120000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>515000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>106000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>205000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>223000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3820,55 +4017,59 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5490000</v>
+      </c>
+      <c r="E83" s="3">
         <v>4984000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6524000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6685000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6253000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>6174000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>7382000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1494000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1305000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1560000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1114000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1104000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1196000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1104000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>985000</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3914,8 +4115,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3961,8 +4165,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4008,8 +4215,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4055,8 +4265,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4102,55 +4315,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3578000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2516000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2014000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-631000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2846000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>124000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1011000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>323000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>884000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>811000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>834000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>269000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>553000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>860000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>991000</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4168,55 +4387,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-268000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-457000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-292000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-299000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-364000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-316000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-222000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-85000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-100000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-106000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-77000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-90000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-112000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-73000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-112000</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4262,8 +4485,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4309,55 +4535,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-234000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-458000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-310000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-257000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-218000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>862000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>2351000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>529000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-26000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-226000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>40000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>156000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-153000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-396000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-84000</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4375,8 +4607,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4422,8 +4655,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4469,8 +4705,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4516,8 +4755,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4563,145 +4805,157 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1529000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2625000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1251000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-432000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1272000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2313000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3570000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-587000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-42000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-273000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-69000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-469000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-277000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-274000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-739000</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>74000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-80000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-15000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>29000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>61000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-56000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-61000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-5000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-37000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-20000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>21000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-70000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>43000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>28000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1889000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-647000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>438000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1291000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1417000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1383000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-269000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>260000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>779000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>292000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>826000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-114000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>166000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>218000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>204000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WBD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WBD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
   <si>
     <t>WBD</t>
   </si>
@@ -656,233 +656,245 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>9958000</v>
+      </c>
+      <c r="E8" s="3">
         <v>10284000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9979000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>10358000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>10700000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>11008000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9823000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9827000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3159000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3187000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3150000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3062000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2792000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2886000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2561000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2541000</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>5932000</v>
+      </c>
+      <c r="E9" s="3">
         <v>5885000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5118000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6608000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6589000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6954000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4718000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6123000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1232000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1065000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1527000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1054000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>969000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1089000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1002000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>804000</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4026000</v>
+      </c>
+      <c r="E10" s="3">
         <v>4399000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4861000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3750000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4111000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4054000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5105000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3704000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1927000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2122000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1623000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2008000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1823000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1797000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1559000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1737000</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -901,8 +913,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -951,8 +964,11 @@
       <c r="R12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1001,108 +1017,117 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>148000</v>
+      </c>
+      <c r="E14" s="3">
         <v>102000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>462000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>185000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>222000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1198000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2430000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1535000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>9000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>5000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>15000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>8000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>18000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>150000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>70000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>122000</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1888000</v>
+      </c>
+      <c r="E15" s="3">
         <v>2024000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1989000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1914000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2058000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2169000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2233000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2266000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>525000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>539000</v>
-      </c>
-      <c r="M15" s="3">
-        <v>341000</v>
       </c>
       <c r="N15" s="3">
         <v>341000</v>
       </c>
       <c r="O15" s="3">
+        <v>341000</v>
+      </c>
+      <c r="P15" s="3">
         <v>361000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>358000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>341000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>334000</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1118,108 +1143,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>10200000</v>
+      </c>
+      <c r="E17" s="3">
         <v>10466000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>9860000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>11269000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>11257000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12902000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12013000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>13466000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2806000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2679000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2827000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2284000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2399000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2406000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2046000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1895000</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-242000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-182000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>119000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-911000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-557000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1894000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2190000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-3639000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>353000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>508000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>323000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>778000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>393000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>480000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>515000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>646000</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1238,258 +1270,274 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-62000</v>
+      </c>
+      <c r="E20" s="3">
         <v>71000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-77000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-110000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-89000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-106000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-94000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>476000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-171000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>69000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>99000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>67000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>109000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-25000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5285000</v>
+      </c>
+      <c r="E21" s="3">
         <v>5379000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5026000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5618000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>6018000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4270000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3878000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3649000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2323000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1642000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1952000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1991000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1564000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1785000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1594000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1613000</v>
       </c>
     </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>515000</v>
+      </c>
+      <c r="E22" s="3">
         <v>502000</v>
-      </c>
-      <c r="E22" s="3">
-        <v>574000</v>
       </c>
       <c r="F22" s="3">
         <v>574000</v>
       </c>
       <c r="G22" s="3">
+        <v>574000</v>
+      </c>
+      <c r="H22" s="3">
         <v>571000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>558000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>555000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>511000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>153000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>154000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>159000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>157000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>163000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>173000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>171000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>172000</v>
       </c>
     </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-819000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-613000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-532000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1480000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1238000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2541000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2851000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-4244000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>676000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>183000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>233000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>720000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>297000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>416000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>319000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>456000</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>136000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-221000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-125000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-260000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-178000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-462000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-566000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-836000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>201000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>92000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>36000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>106000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>98000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-11000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>156000</v>
       </c>
     </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1538,108 +1586,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-955000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-392000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-407000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1220000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1060000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2079000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2285000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3408000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>475000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>91000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>197000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>718000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>191000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>318000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>330000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>300000</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-966000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-400000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-417000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1240000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1069000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2101000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2308000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3418000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>407000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>48000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>120000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>515000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>106000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>205000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>223000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1688,8 +1745,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1738,8 +1798,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1788,8 +1851,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1838,108 +1904,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>62000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-71000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>77000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>110000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>89000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>106000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>94000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-476000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>171000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-69000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-99000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-67000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-109000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>25000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-966000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-400000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-417000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1240000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1069000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2101000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2308000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3418000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>407000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>48000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>120000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>515000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>106000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>205000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>223000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1988,113 +2063,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-966000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-400000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-417000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1240000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1069000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2101000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2308000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3418000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>407000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>48000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>120000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>515000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>106000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>205000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>223000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2113,8 +2197,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2133,58 +2218,62 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2976000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3780000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2383000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3027000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2594000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3731000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2422000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2575000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4162000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3905000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3116000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2834000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2008000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2091000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1893000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1683000</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2233,58 +2322,64 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6303000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6047000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6312000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6770000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6833000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6380000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6669000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7049000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2426000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2446000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2462000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2657000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2476000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2537000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2444000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2473000</v>
       </c>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2333,258 +2428,276 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4623000</v>
+      </c>
+      <c r="E45" s="3">
         <v>4391000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4136000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3976000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4300000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3888000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3581000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5825000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>585000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>913000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1078000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1237000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1381000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1502000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1141000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>561000</v>
       </c>
     </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13902000</v>
+      </c>
+      <c r="E46" s="3">
         <v>14218000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12831000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>13773000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>13727000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>13999000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12672000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>15449000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7173000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7264000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6656000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6728000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5865000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6130000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5478000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4717000</v>
       </c>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
-      </c>
-      <c r="K47" s="3" t="s">
+        <v>967000</v>
+      </c>
+      <c r="E47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K47" s="3">
+        <v>0</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="3">
         <v>543000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>545000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>559000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>522000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>507000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>536000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>530000</v>
       </c>
     </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5937000</v>
+      </c>
+      <c r="E48" s="3">
         <v>9031000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5810000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5473000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5325000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8490000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8365000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8515000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1328000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1336000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1310000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1239000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1189000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1206000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1125000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1088000</v>
       </c>
     </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>91978000</v>
+      </c>
+      <c r="E49" s="3">
         <v>94483000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>97055000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>100888000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>103370000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>106072000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>109482000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>113117000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>22611000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>23061000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>23429000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>23694000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>23765000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>24149000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>24194000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>24618000</v>
       </c>
     </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2633,8 +2746,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2683,58 +2799,64 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7035000</v>
+      </c>
+      <c r="E52" s="3">
         <v>5025000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8053000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8484000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>8162000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5440000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5530000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5159000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2687000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2223000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2378000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2352000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2284000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2095000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2105000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2136000</v>
       </c>
     </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2783,58 +2905,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>119819000</v>
+      </c>
+      <c r="E54" s="3">
         <v>122757000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>123749000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>128618000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>130584000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>134001000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>136049000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>142240000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>33799000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>34427000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>34318000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>34572000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>33625000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>34087000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>33438000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>33089000</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2853,8 +2981,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2873,308 +3002,327 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1245000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1260000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1329000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1689000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1123000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1454000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1534000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1397000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>521000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>412000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2361000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2174000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2128000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>397000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>403000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>367000</v>
       </c>
     </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3430000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1854000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1302000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3001000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3496000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>447000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1338000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1175000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>794000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>397000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>349000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>585000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>351000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>392000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>336000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>339000</v>
       </c>
     </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>12281000</v>
+      </c>
+      <c r="E59" s="3">
         <v>12218000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11957000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>12216000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>11761000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>13116000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>11804000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>11864000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2247000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2650000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>625000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>806000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>663000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2293000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2017000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1870000</v>
       </c>
     </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>16956000</v>
+      </c>
+      <c r="E60" s="3">
         <v>15332000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>14588000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>16906000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>16380000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>15017000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>14676000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>14436000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3562000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3459000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3335000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3565000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3142000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3082000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2756000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2576000</v>
       </c>
     </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>39148000</v>
+      </c>
+      <c r="E61" s="3">
         <v>42080000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>43498000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>44276000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>45434000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>48820000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>48799000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>51594000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>13605000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>14617000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>14436000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>14462000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>14675000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>15253000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>14981000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>14944000</v>
       </c>
     </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>18421000</v>
+      </c>
+      <c r="E62" s="3">
         <v>18873000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>19521000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>20651000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>20928000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>21497000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>22494000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>23263000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3070000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2955000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3149000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3237000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3233000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3369000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3661000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3769000</v>
       </c>
     </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3223,8 +3371,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3273,8 +3424,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3323,58 +3477,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>75668000</v>
+      </c>
+      <c r="E66" s="3">
         <v>77531000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>78975000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>83166000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>84088000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>86906000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>87532000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>90857000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>21830000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>22828000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>22707000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>23034000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>22810000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>23623000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>23351000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>23222000</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3393,8 +3553,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3443,8 +3604,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3493,8 +3657,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3543,8 +3710,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3593,58 +3763,64 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1894000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-928000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-526000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-105000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1133000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2205000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4306000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>6614000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>10033000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9580000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9522000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>9360000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8682000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>8543000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>8278000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7980000</v>
       </c>
     </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3693,8 +3869,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3743,8 +3922,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3793,58 +3975,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>44151000</v>
+      </c>
+      <c r="E76" s="3">
         <v>45226000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>44774000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>45452000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>46496000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>47095000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>48517000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>51383000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11969000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11599000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11611000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11538000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10815000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10464000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>10087000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9867000</v>
       </c>
     </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3893,113 +4081,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-966000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-400000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-417000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1240000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1069000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2101000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2308000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3418000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>407000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>48000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>120000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>515000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>106000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>205000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>223000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4018,58 +4215,62 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5589000</v>
+      </c>
+      <c r="E83" s="3">
         <v>5490000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4984000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6524000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6685000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>6253000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>6174000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>7382000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1494000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1305000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1560000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1114000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1104000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1196000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1104000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>985000</v>
       </c>
     </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4118,8 +4319,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4168,8 +4372,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4218,8 +4425,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4268,8 +4478,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4318,58 +4531,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>585000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3578000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2516000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2014000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-631000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2846000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>124000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1011000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>323000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>884000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>811000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>834000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>269000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>553000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>860000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>991000</v>
       </c>
     </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4388,58 +4607,62 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-195000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-268000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-457000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-292000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-299000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-364000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-316000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-222000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-85000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-100000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-106000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-77000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-90000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-112000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-73000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-112000</v>
       </c>
     </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4488,8 +4711,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4538,58 +4764,64 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-207000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-234000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-458000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-310000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-257000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-218000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>862000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>2351000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>529000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-26000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-226000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>40000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>156000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-153000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-396000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-84000</v>
       </c>
     </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4608,8 +4840,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4658,8 +4891,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4708,8 +4944,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4758,8 +4997,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4808,154 +5050,166 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1237000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1529000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2625000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1251000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-432000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1272000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2313000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3570000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-587000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-42000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-273000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-69000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-469000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-277000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-274000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-739000</v>
       </c>
     </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-74000</v>
+      </c>
+      <c r="E101" s="3">
         <v>74000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-80000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-15000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>29000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>61000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-56000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-61000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-5000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-37000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-20000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>21000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-70000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>43000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>28000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-933000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1889000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-647000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>438000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1291000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1417000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1383000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-269000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>260000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>779000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>292000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>826000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-114000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>166000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>218000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>204000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WBD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WBD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
   <si>
     <t>WBD</t>
   </si>
@@ -656,245 +656,257 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>9713000</v>
+      </c>
+      <c r="E8" s="3">
         <v>9958000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>10284000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9979000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>10358000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>10700000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>11008000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9823000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9827000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3159000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3187000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3150000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3062000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2792000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2886000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2561000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2541000</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>6152000</v>
+      </c>
+      <c r="E9" s="3">
         <v>5932000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5885000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5118000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6608000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6589000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6954000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4718000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6123000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1232000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1065000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1527000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1054000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>969000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1089000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1002000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>804000</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3561000</v>
+      </c>
+      <c r="E10" s="3">
         <v>4026000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4399000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4861000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3750000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4111000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4054000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5105000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3704000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1927000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2122000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1623000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2008000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1823000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1797000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1559000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1737000</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -914,8 +926,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -967,8 +980,11 @@
       <c r="S12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1020,114 +1036,123 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>9022000</v>
+      </c>
+      <c r="E14" s="3">
         <v>148000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>102000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>462000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>185000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>222000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1198000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2430000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1535000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>9000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>5000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>15000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>8000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>18000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>150000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>70000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>122000</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1744000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1888000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2024000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1989000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1914000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2058000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2169000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2233000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2266000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>525000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>539000</v>
-      </c>
-      <c r="N15" s="3">
-        <v>341000</v>
       </c>
       <c r="O15" s="3">
         <v>341000</v>
       </c>
       <c r="P15" s="3">
+        <v>341000</v>
+      </c>
+      <c r="Q15" s="3">
         <v>361000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>358000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>341000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>334000</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1144,114 +1169,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>19379000</v>
+      </c>
+      <c r="E17" s="3">
         <v>10200000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10466000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9860000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>11269000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>11257000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12902000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>12013000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>13466000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2806000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2679000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2827000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2284000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2399000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2406000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2046000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1895000</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-9666000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-242000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-182000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>119000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-911000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-557000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1894000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2190000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3639000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>353000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>508000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>323000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>778000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>393000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>480000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>515000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>646000</v>
       </c>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1271,273 +1303,289 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>149000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-62000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>71000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-77000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>5000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-110000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-89000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-106000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-94000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>476000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-171000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>69000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>99000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>67000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>109000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-25000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3905000</v>
+      </c>
+      <c r="E21" s="3">
         <v>5285000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5379000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5026000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5618000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>6018000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4270000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3878000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3649000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2323000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1642000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1952000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1991000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1564000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1785000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1594000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1613000</v>
       </c>
     </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>518000</v>
+      </c>
+      <c r="E22" s="3">
         <v>515000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>502000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>574000</v>
       </c>
       <c r="G22" s="3">
         <v>574000</v>
       </c>
       <c r="H22" s="3">
+        <v>574000</v>
+      </c>
+      <c r="I22" s="3">
         <v>571000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>558000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>555000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>511000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>153000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>154000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>159000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>157000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>163000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>173000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>171000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>172000</v>
       </c>
     </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-10035000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-819000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-613000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-532000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1480000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1238000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2541000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2851000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-4244000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>676000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>183000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>233000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>720000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>297000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>416000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>319000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>456000</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E24" s="3">
         <v>136000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-221000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-125000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-260000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-178000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-462000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-566000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-836000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>201000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>92000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>36000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>106000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>98000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-11000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>156000</v>
       </c>
     </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1589,114 +1637,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-10028000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-955000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-392000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-407000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1220000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1060000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2079000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2285000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3408000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>475000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>91000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>197000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>718000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>191000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>318000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>330000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>300000</v>
       </c>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9986000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-966000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-400000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-417000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1240000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1069000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2101000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2308000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3418000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>407000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>48000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>120000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>515000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>106000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>205000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>223000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1748,8 +1805,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1801,8 +1861,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1854,8 +1917,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1907,114 +1973,123 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-149000</v>
+      </c>
+      <c r="E32" s="3">
         <v>62000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-71000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>77000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-5000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>110000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>89000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>106000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>94000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-476000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>171000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-69000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-99000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-67000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-109000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>25000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9986000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-966000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-400000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-417000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1240000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1069000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2101000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2308000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3418000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>407000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>48000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>120000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>515000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>106000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>205000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>223000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2066,119 +2141,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9986000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-966000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-400000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-417000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1240000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1069000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2101000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2308000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3418000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>407000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>48000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>120000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>515000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>106000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>205000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>223000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2198,8 +2282,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2219,61 +2304,65 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3613000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2976000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3780000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2383000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3027000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2594000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3731000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2422000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2575000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4162000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3905000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3116000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2834000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2008000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2091000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1893000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1683000</v>
       </c>
     </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2325,61 +2414,67 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6166000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6303000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6047000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6312000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6770000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6833000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6380000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6669000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7049000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2426000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2446000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2462000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2657000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2476000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2537000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2444000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2473000</v>
       </c>
     </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2431,122 +2526,131 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3651000</v>
+      </c>
+      <c r="E45" s="3">
         <v>4623000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4391000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4136000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3976000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4300000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3888000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3581000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5825000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>585000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>913000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1078000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1237000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1381000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1502000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1141000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>561000</v>
       </c>
     </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13430000</v>
+      </c>
+      <c r="E46" s="3">
         <v>13902000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>14218000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12831000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>13773000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>13727000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>13999000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>12672000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>15449000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7173000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7264000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6656000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6728000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5865000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6130000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5478000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4717000</v>
       </c>
     </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>856000</v>
+      </c>
+      <c r="E47" s="3">
         <v>967000</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>8</v>
@@ -2563,141 +2667,150 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3" t="s">
+      <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N47" s="3">
         <v>543000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>545000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>559000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>522000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>507000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>536000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>530000</v>
       </c>
     </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6043000</v>
+      </c>
+      <c r="E48" s="3">
         <v>5937000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9031000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5810000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5473000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5325000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8490000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8365000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8515000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1328000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1336000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1310000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1239000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1189000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1206000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1125000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1088000</v>
       </c>
     </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>80907000</v>
+      </c>
+      <c r="E49" s="3">
         <v>91978000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>94483000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>97055000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>100888000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>103370000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>106072000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>109482000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>113117000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>22611000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>23061000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>23429000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>23694000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>23765000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>24149000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>24194000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>24618000</v>
       </c>
     </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2749,8 +2862,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2802,61 +2918,67 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6793000</v>
+      </c>
+      <c r="E52" s="3">
         <v>7035000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5025000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8053000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>8484000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>8162000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5440000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5530000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5159000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2687000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2223000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2378000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2352000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2284000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2095000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2105000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2136000</v>
       </c>
     </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2908,61 +3030,67 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>108029000</v>
+      </c>
+      <c r="E54" s="3">
         <v>119819000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>122757000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>123749000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>128618000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>130584000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>134001000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>136049000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>142240000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>33799000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>34427000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>34318000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>34572000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>33625000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>34087000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>33438000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>33089000</v>
       </c>
     </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2982,8 +3110,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3003,326 +3132,345 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1151000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1245000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1260000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1329000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1689000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1123000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1454000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1534000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1397000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>521000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>412000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2361000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2174000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2128000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>397000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>403000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>367000</v>
       </c>
     </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3669000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3430000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1854000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1302000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3001000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3496000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>447000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1338000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1175000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>794000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>397000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>349000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>585000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>351000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>392000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>336000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>339000</v>
       </c>
     </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>12948000</v>
+      </c>
+      <c r="E59" s="3">
         <v>12281000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>12218000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>11957000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12216000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>11761000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>13116000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>11804000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11864000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2247000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2650000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>625000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>806000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>663000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2293000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2017000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1870000</v>
       </c>
     </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>17768000</v>
+      </c>
+      <c r="E60" s="3">
         <v>16956000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>15332000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>14588000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>16906000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>16380000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>15017000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>14676000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>14436000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3562000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3459000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3335000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3565000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3142000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3082000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2756000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2576000</v>
       </c>
     </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>37289000</v>
+      </c>
+      <c r="E61" s="3">
         <v>39148000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>42080000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>43498000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>44276000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>45434000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>48820000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>48799000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>51594000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>13605000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>14617000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>14436000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>14462000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>14675000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>15253000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>14981000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>14944000</v>
       </c>
     </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>17557000</v>
+      </c>
+      <c r="E62" s="3">
         <v>18421000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>18873000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>19521000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>20651000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>20928000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>21497000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>22494000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>23263000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3070000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2955000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3149000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3237000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3233000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3369000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3661000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3769000</v>
       </c>
     </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3374,8 +3522,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3427,8 +3578,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3480,61 +3634,67 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>73684000</v>
+      </c>
+      <c r="E66" s="3">
         <v>75668000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>77531000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>78975000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>83166000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>84088000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>86906000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>87532000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>90857000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>21830000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>22828000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>22707000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>23034000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>22810000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>23623000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>23351000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>23222000</v>
       </c>
     </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3554,8 +3714,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3607,8 +3768,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3660,8 +3824,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3713,8 +3880,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3766,61 +3936,67 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-11880000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1894000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-928000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-526000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-105000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1133000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2205000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4306000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6614000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>10033000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9580000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>9522000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9360000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>8682000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>8543000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>8278000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7980000</v>
       </c>
     </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3872,8 +4048,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3925,8 +4104,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3978,61 +4160,67 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>34345000</v>
+      </c>
+      <c r="E76" s="3">
         <v>44151000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>45226000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>44774000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>45452000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>46496000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>47095000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>48517000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>51383000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11969000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11599000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11611000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11538000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10815000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>10464000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>10087000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9867000</v>
       </c>
     </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4084,119 +4272,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9986000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-966000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-400000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-417000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1240000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1069000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2101000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2308000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3418000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>407000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>48000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>120000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>515000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>106000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>205000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>223000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4216,61 +4413,65 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5612000</v>
+      </c>
+      <c r="E83" s="3">
         <v>5589000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5490000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4984000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6524000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>6685000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>6253000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>6174000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>7382000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1494000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1305000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1560000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1114000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1104000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1196000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1104000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>985000</v>
       </c>
     </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4322,8 +4523,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4375,8 +4579,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4428,8 +4635,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4481,8 +4691,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4534,61 +4747,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1228000</v>
+      </c>
+      <c r="E89" s="3">
         <v>585000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3578000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2516000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2014000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-631000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2846000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>124000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1011000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>323000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>884000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>811000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>834000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>269000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>553000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>860000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>991000</v>
       </c>
     </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4608,61 +4827,65 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-252000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-195000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-268000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-457000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-292000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-299000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-364000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-316000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-222000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-85000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-100000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-106000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-77000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-90000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-112000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-73000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-112000</v>
       </c>
     </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4714,8 +4937,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4767,61 +4993,67 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>70000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-207000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-234000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-458000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-310000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-257000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-218000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>862000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>2351000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>529000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-26000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-226000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>40000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>156000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-153000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-396000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-84000</v>
       </c>
     </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4841,8 +5073,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4894,8 +5127,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4947,8 +5183,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5000,8 +5239,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5053,163 +5295,175 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1037000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1237000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1529000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2625000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1251000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-432000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1272000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2313000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3570000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-587000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-42000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-273000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-69000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-469000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-277000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-274000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-739000</v>
       </c>
     </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-74000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>74000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-80000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-15000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>29000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>61000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-56000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-61000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-5000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-37000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-20000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>21000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-70000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>43000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>28000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>231000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-933000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1889000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-647000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>438000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1291000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1417000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1383000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-269000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>260000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>779000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>292000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>826000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-114000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>166000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>218000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>204000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WBD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WBD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
   <si>
     <t>WBD</t>
   </si>
@@ -656,257 +656,269 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>9623000</v>
+      </c>
+      <c r="E8" s="3">
         <v>9713000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9958000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>10284000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9979000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>10358000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>10700000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>11008000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9823000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9827000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3159000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3187000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3150000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3062000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2792000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2886000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2561000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2541000</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>6152000</v>
+        <v>5036000</v>
       </c>
       <c r="E9" s="3">
-        <v>5932000</v>
+        <v>6204000</v>
       </c>
       <c r="F9" s="3">
-        <v>5885000</v>
+        <v>6058000</v>
       </c>
       <c r="G9" s="3">
+        <v>5685000</v>
+      </c>
+      <c r="H9" s="3">
         <v>5118000</v>
       </c>
-      <c r="H9" s="3">
-        <v>6608000</v>
-      </c>
       <c r="I9" s="3">
+        <v>6636000</v>
+      </c>
+      <c r="J9" s="3">
         <v>6589000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6954000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4718000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6123000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1232000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1065000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1527000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1054000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>969000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1089000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1002000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>804000</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>3561000</v>
+        <v>4587000</v>
       </c>
       <c r="E10" s="3">
-        <v>4026000</v>
+        <v>3509000</v>
       </c>
       <c r="F10" s="3">
-        <v>4399000</v>
+        <v>3900000</v>
       </c>
       <c r="G10" s="3">
+        <v>4599000</v>
+      </c>
+      <c r="H10" s="3">
         <v>4861000</v>
       </c>
-      <c r="H10" s="3">
-        <v>3750000</v>
-      </c>
       <c r="I10" s="3">
+        <v>3722000</v>
+      </c>
+      <c r="J10" s="3">
         <v>4111000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4054000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5105000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3704000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1927000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2122000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1623000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2008000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1823000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1797000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1559000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1737000</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -927,8 +939,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -983,8 +996,11 @@
       <c r="T12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1039,120 +1055,129 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>9022000</v>
+        <v>174000</v>
       </c>
       <c r="E14" s="3">
-        <v>148000</v>
+        <v>8832000</v>
       </c>
       <c r="F14" s="3">
-        <v>102000</v>
+        <v>118000</v>
       </c>
       <c r="G14" s="3">
-        <v>462000</v>
+        <v>323000</v>
       </c>
       <c r="H14" s="3">
-        <v>185000</v>
+        <v>495000</v>
       </c>
       <c r="I14" s="3">
-        <v>222000</v>
+        <v>215000</v>
       </c>
       <c r="J14" s="3">
+        <v>308000</v>
+      </c>
+      <c r="K14" s="3">
         <v>1198000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2430000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1535000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>9000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>5000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>15000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>8000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>18000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>150000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>70000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>122000</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1762000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1744000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1888000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2024000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1989000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1914000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2058000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2169000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2233000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2266000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>525000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>539000</v>
-      </c>
-      <c r="O15" s="3">
-        <v>341000</v>
       </c>
       <c r="P15" s="3">
         <v>341000</v>
       </c>
       <c r="Q15" s="3">
+        <v>341000</v>
+      </c>
+      <c r="R15" s="3">
         <v>361000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>358000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>341000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>334000</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1170,120 +1195,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>19379000</v>
+        <v>9121000</v>
       </c>
       <c r="E17" s="3">
-        <v>10200000</v>
+        <v>10365000</v>
       </c>
       <c r="F17" s="3">
-        <v>10466000</v>
+        <v>10118000</v>
       </c>
       <c r="G17" s="3">
-        <v>9860000</v>
+        <v>10110000</v>
       </c>
       <c r="H17" s="3">
-        <v>11269000</v>
+        <v>9385000</v>
       </c>
       <c r="I17" s="3">
-        <v>11257000</v>
+        <v>11127000</v>
       </c>
       <c r="J17" s="3">
+        <v>10988000</v>
+      </c>
+      <c r="K17" s="3">
         <v>12902000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>12013000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>13466000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2806000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2679000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2827000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2284000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2399000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2406000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2046000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1895000</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-9666000</v>
+        <v>502000</v>
       </c>
       <c r="E18" s="3">
-        <v>-242000</v>
+        <v>-652000</v>
       </c>
       <c r="F18" s="3">
-        <v>-182000</v>
+        <v>-160000</v>
       </c>
       <c r="G18" s="3">
-        <v>119000</v>
+        <v>174000</v>
       </c>
       <c r="H18" s="3">
-        <v>-911000</v>
+        <v>594000</v>
       </c>
       <c r="I18" s="3">
-        <v>-557000</v>
+        <v>-769000</v>
       </c>
       <c r="J18" s="3">
+        <v>-288000</v>
+      </c>
+      <c r="K18" s="3">
         <v>-1894000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2190000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3639000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>353000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>508000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>323000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>778000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>393000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>480000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>515000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>646000</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1304,288 +1336,304 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>149000</v>
+        <v>38000</v>
       </c>
       <c r="E20" s="3">
-        <v>-62000</v>
+        <v>92000</v>
       </c>
       <c r="F20" s="3">
-        <v>71000</v>
+        <v>103000</v>
       </c>
       <c r="G20" s="3">
-        <v>-77000</v>
+        <v>-25000</v>
       </c>
       <c r="H20" s="3">
-        <v>5000</v>
+        <v>124000</v>
       </c>
       <c r="I20" s="3">
-        <v>-110000</v>
+        <v>18000</v>
       </c>
       <c r="J20" s="3">
+        <v>111000</v>
+      </c>
+      <c r="K20" s="3">
         <v>-89000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-106000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-94000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>476000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-171000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>69000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>99000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>67000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>109000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-25000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-3905000</v>
+        <v>2226000</v>
       </c>
       <c r="E21" s="3">
-        <v>5285000</v>
+        <v>1000000</v>
       </c>
       <c r="F21" s="3">
-        <v>5379000</v>
+        <v>1625000</v>
       </c>
       <c r="G21" s="3">
-        <v>5026000</v>
+        <v>2223000</v>
       </c>
       <c r="H21" s="3">
-        <v>5618000</v>
+        <v>2459000</v>
       </c>
       <c r="I21" s="3">
-        <v>6018000</v>
+        <v>1127000</v>
       </c>
       <c r="J21" s="3">
+        <v>1659000</v>
+      </c>
+      <c r="K21" s="3">
         <v>4270000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3878000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3649000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2323000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1642000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1952000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1991000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1564000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1785000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1594000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1613000</v>
       </c>
     </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>517000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>522000</v>
+      </c>
+      <c r="F22" s="3">
+        <v>498000</v>
+      </c>
+      <c r="G22" s="3">
+        <v>540000</v>
+      </c>
+      <c r="H22" s="3">
+        <v>550000</v>
+      </c>
+      <c r="I22" s="3">
         <v>518000</v>
       </c>
-      <c r="E22" s="3">
-        <v>515000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>502000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>574000</v>
-      </c>
-      <c r="H22" s="3">
-        <v>574000</v>
-      </c>
-      <c r="I22" s="3">
-        <v>571000</v>
-      </c>
       <c r="J22" s="3">
+        <v>576000</v>
+      </c>
+      <c r="K22" s="3">
         <v>558000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>555000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>511000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>153000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>154000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>159000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>157000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>163000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>173000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>171000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>172000</v>
       </c>
     </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-178000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-10035000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-819000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-613000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-532000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1480000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1238000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2541000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2851000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-4244000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>676000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>183000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>233000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>720000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>297000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>416000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>319000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>456000</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-319000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-7000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>136000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-221000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-125000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-260000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-178000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-462000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-566000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-836000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>201000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>92000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>36000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>106000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>98000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-11000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>156000</v>
       </c>
     </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1640,120 +1688,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>141000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-10028000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-955000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-392000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-407000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1220000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1060000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2079000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2285000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3408000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>475000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>91000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>197000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>718000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>191000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>318000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>330000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>300000</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>135000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-9986000</v>
       </c>
-      <c r="E27" s="3">
-        <v>-966000</v>
-      </c>
       <c r="F27" s="3">
+        <v>-970000</v>
+      </c>
+      <c r="G27" s="3">
         <v>-400000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-417000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1240000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1069000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2101000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2308000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3418000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>407000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>48000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>120000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>515000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>106000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>205000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>223000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1808,8 +1865,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1864,8 +1924,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1920,8 +1983,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1976,120 +2042,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-149000</v>
+        <v>-38000</v>
       </c>
       <c r="E32" s="3">
-        <v>62000</v>
+        <v>-92000</v>
       </c>
       <c r="F32" s="3">
-        <v>-71000</v>
+        <v>-103000</v>
       </c>
       <c r="G32" s="3">
-        <v>77000</v>
+        <v>25000</v>
       </c>
       <c r="H32" s="3">
-        <v>-5000</v>
+        <v>-124000</v>
       </c>
       <c r="I32" s="3">
-        <v>110000</v>
+        <v>-18000</v>
       </c>
       <c r="J32" s="3">
+        <v>-111000</v>
+      </c>
+      <c r="K32" s="3">
         <v>89000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>106000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>94000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-476000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>171000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-69000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-99000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-67000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-109000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>25000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>135000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-9986000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-966000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-400000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-417000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1240000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1069000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2101000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2308000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3418000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>407000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>48000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>120000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>515000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>106000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>205000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>223000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2144,125 +2219,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>135000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-9986000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-966000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-400000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-417000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1240000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1069000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2101000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2308000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3418000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>407000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>48000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>120000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>515000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>106000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>205000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>223000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2283,8 +2367,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2305,87 +2390,91 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3336000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3613000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2976000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3780000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2383000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3027000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2594000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3731000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2422000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2575000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4162000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3905000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3116000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2834000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2008000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2091000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1893000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1683000</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>68000</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>93000</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>83000</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>72000</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2417,87 +2506,93 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>6166000</v>
+        <v>3498000</v>
       </c>
       <c r="E43" s="3">
-        <v>6303000</v>
+        <v>3599000</v>
       </c>
       <c r="F43" s="3">
-        <v>6047000</v>
+        <v>3643000</v>
       </c>
       <c r="G43" s="3">
-        <v>6312000</v>
+        <v>4532000</v>
       </c>
       <c r="H43" s="3">
-        <v>6770000</v>
+        <v>3683000</v>
       </c>
       <c r="I43" s="3">
-        <v>6833000</v>
+        <v>3485000</v>
       </c>
       <c r="J43" s="3">
+        <v>3558000</v>
+      </c>
+      <c r="K43" s="3">
         <v>6380000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6669000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7049000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2426000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2446000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2462000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2657000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2476000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2537000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2444000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2473000</v>
       </c>
     </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2529,288 +2624,306 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3651000</v>
+        <v>2140000</v>
       </c>
       <c r="E45" s="3">
-        <v>4623000</v>
+        <v>2659000</v>
       </c>
       <c r="F45" s="3">
-        <v>4391000</v>
+        <v>2742000</v>
       </c>
       <c r="G45" s="3">
-        <v>4136000</v>
+        <v>2906000</v>
       </c>
       <c r="H45" s="3">
-        <v>3976000</v>
+        <v>2755000</v>
       </c>
       <c r="I45" s="3">
-        <v>4300000</v>
+        <v>3607000</v>
       </c>
       <c r="J45" s="3">
+        <v>3374000</v>
+      </c>
+      <c r="K45" s="3">
         <v>3888000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3581000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5825000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>585000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>913000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1078000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1237000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1381000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1502000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1141000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>561000</v>
       </c>
     </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12505000</v>
+      </c>
+      <c r="E46" s="3">
         <v>13430000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>13902000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>14218000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>12831000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>13773000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>13727000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>13999000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>12672000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>15449000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7173000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7264000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6656000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6728000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5865000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6130000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5478000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4717000</v>
       </c>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>856000</v>
+        <v>1257000</v>
       </c>
       <c r="E47" s="3">
-        <v>967000</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
+        <v>1301000</v>
+      </c>
+      <c r="F47" s="3">
+        <v>1437000</v>
+      </c>
+      <c r="G47" s="3">
+        <v>1470000</v>
+      </c>
+      <c r="H47" s="3">
+        <v>1443000</v>
+      </c>
+      <c r="I47" s="3">
+        <v>1491000</v>
+      </c>
+      <c r="J47" s="3">
+        <v>1499000</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
-      <c r="M47" s="3" t="s">
+      <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="3">
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O47" s="3">
         <v>543000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>545000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>559000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>522000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>507000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>536000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>530000</v>
       </c>
     </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6158000</v>
+      </c>
+      <c r="E48" s="3">
         <v>6043000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5937000</v>
       </c>
-      <c r="F48" s="3">
-        <v>9031000</v>
-      </c>
       <c r="G48" s="3">
+        <v>7730000</v>
+      </c>
+      <c r="H48" s="3">
         <v>5810000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5473000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5325000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8490000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8365000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8515000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1328000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1336000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1310000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1239000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1189000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1206000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1125000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1088000</v>
       </c>
     </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>79675000</v>
+      </c>
+      <c r="E49" s="3">
         <v>80907000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>91978000</v>
       </c>
-      <c r="F49" s="3">
-        <v>94483000</v>
-      </c>
       <c r="G49" s="3">
+        <v>95784000</v>
+      </c>
+      <c r="H49" s="3">
         <v>97055000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>100888000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>103370000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>106072000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>109482000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>113117000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>22611000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>23061000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>23429000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>23694000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>23765000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>24149000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>24194000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>24618000</v>
       </c>
     </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2865,8 +2978,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2921,64 +3037,70 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>6793000</v>
+        <v>6738000</v>
       </c>
       <c r="E52" s="3">
-        <v>7035000</v>
+        <v>6348000</v>
       </c>
       <c r="F52" s="3">
-        <v>5025000</v>
+        <v>6565000</v>
       </c>
       <c r="G52" s="3">
-        <v>8053000</v>
+        <v>2858000</v>
       </c>
       <c r="H52" s="3">
-        <v>8484000</v>
+        <v>6610000</v>
       </c>
       <c r="I52" s="3">
-        <v>8162000</v>
+        <v>6993000</v>
       </c>
       <c r="J52" s="3">
+        <v>6663000</v>
+      </c>
+      <c r="K52" s="3">
         <v>5440000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5530000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5159000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2687000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2223000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2378000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2352000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2284000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2095000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2105000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2136000</v>
       </c>
     </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3033,64 +3155,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>106333000</v>
+      </c>
+      <c r="E54" s="3">
         <v>108029000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>119819000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>122757000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>123749000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>128618000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>130584000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>134001000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>136049000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>142240000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>33799000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>34427000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>34318000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>34572000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>33625000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>34087000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>33438000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>33089000</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3111,8 +3239,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3133,344 +3262,363 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1120000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1151000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1245000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1260000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1329000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1689000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1123000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1454000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1534000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1397000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>521000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>412000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2361000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2174000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2128000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>397000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>403000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>367000</v>
       </c>
     </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3043000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3669000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3430000</v>
       </c>
-      <c r="F58" s="3">
-        <v>1854000</v>
-      </c>
       <c r="G58" s="3">
+        <v>2186000</v>
+      </c>
+      <c r="H58" s="3">
         <v>1302000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3001000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3496000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>447000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1338000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1175000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>794000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>397000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>349000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>585000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>351000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>392000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>336000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>339000</v>
       </c>
     </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>12948000</v>
+        <v>1788000</v>
       </c>
       <c r="E59" s="3">
-        <v>12281000</v>
+        <v>2375000</v>
       </c>
       <c r="F59" s="3">
-        <v>12218000</v>
+        <v>2312000</v>
       </c>
       <c r="G59" s="3">
-        <v>11957000</v>
+        <v>1924000</v>
       </c>
       <c r="H59" s="3">
-        <v>12216000</v>
+        <v>2431000</v>
       </c>
       <c r="I59" s="3">
-        <v>11761000</v>
+        <v>2020000</v>
       </c>
       <c r="J59" s="3">
+        <v>2099000</v>
+      </c>
+      <c r="K59" s="3">
         <v>13116000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11804000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11864000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2247000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2650000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>625000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>806000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>663000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2293000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2017000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1870000</v>
       </c>
     </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>15695000</v>
+      </c>
+      <c r="E60" s="3">
         <v>17768000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>16956000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>15332000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>14588000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>16906000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>16380000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>15017000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>14676000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>14436000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3562000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3459000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3335000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3565000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3142000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3082000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2756000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2576000</v>
       </c>
     </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>37289000</v>
+        <v>37166000</v>
       </c>
       <c r="E61" s="3">
-        <v>39148000</v>
+        <v>37293000</v>
       </c>
       <c r="F61" s="3">
-        <v>42080000</v>
+        <v>39155000</v>
       </c>
       <c r="G61" s="3">
-        <v>43498000</v>
+        <v>45104000</v>
       </c>
       <c r="H61" s="3">
-        <v>44276000</v>
+        <v>43504000</v>
       </c>
       <c r="I61" s="3">
-        <v>45434000</v>
+        <v>44289000</v>
       </c>
       <c r="J61" s="3">
+        <v>45435000</v>
+      </c>
+      <c r="K61" s="3">
         <v>48820000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>48799000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>51594000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>13605000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>14617000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>14436000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>14462000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>14675000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>15253000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>14981000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>14944000</v>
       </c>
     </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>17557000</v>
+        <v>9769000</v>
       </c>
       <c r="E62" s="3">
-        <v>18421000</v>
+        <v>9532000</v>
       </c>
       <c r="F62" s="3">
-        <v>18873000</v>
+        <v>9892000</v>
       </c>
       <c r="G62" s="3">
-        <v>19521000</v>
+        <v>6689000</v>
       </c>
       <c r="H62" s="3">
-        <v>20651000</v>
+        <v>10275000</v>
       </c>
       <c r="I62" s="3">
-        <v>20928000</v>
+        <v>10527000</v>
       </c>
       <c r="J62" s="3">
+        <v>10337000</v>
+      </c>
+      <c r="K62" s="3">
         <v>21497000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>22494000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>23263000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3070000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2955000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3149000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3237000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3233000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3369000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3661000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3769000</v>
       </c>
     </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3525,8 +3673,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3581,8 +3732,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3637,64 +3791,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>73684000</v>
+        <v>70159000</v>
       </c>
       <c r="E66" s="3">
-        <v>75668000</v>
+        <v>72614000</v>
       </c>
       <c r="F66" s="3">
-        <v>77531000</v>
+        <v>74525000</v>
       </c>
       <c r="G66" s="3">
-        <v>78975000</v>
+        <v>76285000</v>
       </c>
       <c r="H66" s="3">
-        <v>83166000</v>
+        <v>77607000</v>
       </c>
       <c r="I66" s="3">
-        <v>84088000</v>
+        <v>81833000</v>
       </c>
       <c r="J66" s="3">
+        <v>82742000</v>
+      </c>
+      <c r="K66" s="3">
         <v>86906000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>87532000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>90857000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>21830000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>22828000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>22707000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>23034000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>22810000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>23623000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>23351000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>23222000</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3715,8 +3875,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3771,8 +3932,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3827,8 +3991,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3883,8 +4050,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3939,64 +4109,70 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-11745000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-11880000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1894000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-928000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-526000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-105000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1133000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2205000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4306000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6614000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>10033000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>9580000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9522000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9360000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>8682000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>8543000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>8278000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7980000</v>
       </c>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4051,8 +4227,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4107,8 +4286,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4163,64 +4345,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>35100000</v>
+      </c>
+      <c r="E76" s="3">
         <v>34345000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>44151000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>45226000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>44774000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>45452000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>46496000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>47095000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>48517000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>51383000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11969000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11599000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11611000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11538000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>10815000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>10464000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>10087000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9867000</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4275,125 +4463,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>135000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-9986000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-966000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-400000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-417000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1240000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1069000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2101000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2308000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3418000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>407000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>48000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>120000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>515000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>106000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>205000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>223000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4414,64 +4611,68 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>5612000</v>
+        <v>1989000</v>
       </c>
       <c r="E83" s="3">
-        <v>5589000</v>
+        <v>1914000</v>
       </c>
       <c r="F83" s="3">
-        <v>5490000</v>
+        <v>2058000</v>
       </c>
       <c r="G83" s="3">
-        <v>4984000</v>
+        <v>2169000</v>
       </c>
       <c r="H83" s="3">
-        <v>6524000</v>
+        <v>2233000</v>
       </c>
       <c r="I83" s="3">
-        <v>6685000</v>
+        <v>2266000</v>
       </c>
       <c r="J83" s="3">
+        <v>525000</v>
+      </c>
+      <c r="K83" s="3">
         <v>6253000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6174000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>7382000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1494000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1305000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1560000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1114000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1104000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1196000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1104000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>985000</v>
       </c>
     </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4526,8 +4727,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4582,8 +4786,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4638,8 +4845,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4694,8 +4904,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4750,64 +4963,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>847000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1228000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>585000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3578000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2516000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2014000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-631000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2846000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>124000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1011000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>323000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>884000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>811000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>834000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>269000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>553000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>860000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>991000</v>
       </c>
     </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4828,64 +5047,68 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-215000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-252000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-195000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-268000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-457000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-292000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-299000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-364000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-316000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-222000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-85000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-106000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-77000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-90000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-112000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-73000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-112000</v>
       </c>
     </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4940,8 +5163,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4996,64 +5222,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-218000</v>
+      </c>
+      <c r="E94" s="3">
         <v>70000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-207000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-234000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-458000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-310000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-257000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-218000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>862000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>2351000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>529000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-26000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-226000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>40000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>156000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-153000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-396000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-84000</v>
       </c>
     </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5074,31 +5306,32 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5130,8 +5363,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5186,8 +5422,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5242,8 +5481,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5298,172 +5540,184 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-875000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1037000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1237000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1529000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2625000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1251000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-432000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1272000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2313000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3570000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-587000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-42000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-273000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-69000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-469000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-277000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-274000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-739000</v>
       </c>
     </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-30000</v>
+        <v>-80000</v>
       </c>
       <c r="E101" s="3">
-        <v>-74000</v>
+        <v>-15000</v>
       </c>
       <c r="F101" s="3">
-        <v>74000</v>
+        <v>29000</v>
       </c>
       <c r="G101" s="3">
-        <v>-80000</v>
+        <v>61000</v>
       </c>
       <c r="H101" s="3">
-        <v>-15000</v>
+        <v>-56000</v>
       </c>
       <c r="I101" s="3">
-        <v>29000</v>
+        <v>-61000</v>
       </c>
       <c r="J101" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="K101" s="3">
         <v>61000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-56000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-61000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-5000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-37000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-20000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>21000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-70000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>43000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>28000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-127000</v>
+      </c>
+      <c r="E102" s="3">
         <v>231000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-933000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1889000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-647000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>438000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1291000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1417000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1383000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-269000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>260000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>779000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>292000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>826000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-114000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>166000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>218000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>204000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WBD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WBD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
   <si>
     <t>WBD</t>
   </si>
@@ -656,269 +656,281 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>10027000</v>
+      </c>
+      <c r="E8" s="3">
         <v>9623000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9713000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9958000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>10284000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9979000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>10358000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>10700000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>11008000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9823000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9827000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3159000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3187000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3150000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3062000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2792000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2886000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2561000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2541000</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>5457000</v>
+      </c>
+      <c r="E9" s="3">
         <v>5036000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6204000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6058000</v>
       </c>
-      <c r="G9" s="3">
-        <v>5685000</v>
-      </c>
       <c r="H9" s="3">
+        <v>6000000</v>
+      </c>
+      <c r="I9" s="3">
         <v>5118000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6636000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6589000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6954000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4718000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6123000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1232000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1065000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1527000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1054000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>969000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1089000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1002000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>804000</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4570000</v>
+      </c>
+      <c r="E10" s="3">
         <v>4587000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3509000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3900000</v>
       </c>
-      <c r="G10" s="3">
-        <v>4599000</v>
-      </c>
       <c r="H10" s="3">
+        <v>4284000</v>
+      </c>
+      <c r="I10" s="3">
         <v>4861000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3722000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4111000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4054000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5105000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3704000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1927000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2122000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1623000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2008000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1823000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1797000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1559000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1737000</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -940,8 +952,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -999,8 +1012,11 @@
       <c r="U12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1058,126 +1074,135 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>569000</v>
+      </c>
+      <c r="E14" s="3">
         <v>174000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>8832000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>118000</v>
       </c>
-      <c r="G14" s="3">
-        <v>323000</v>
-      </c>
       <c r="H14" s="3">
+        <v>8000</v>
+      </c>
+      <c r="I14" s="3">
         <v>495000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>215000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>308000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1198000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2430000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1535000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>9000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>5000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>15000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>8000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>18000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>150000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>70000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>122000</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1643000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1762000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1744000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1888000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2024000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1989000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1914000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2058000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2169000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2233000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2266000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>525000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>539000</v>
-      </c>
-      <c r="P15" s="3">
-        <v>341000</v>
       </c>
       <c r="Q15" s="3">
         <v>341000</v>
       </c>
       <c r="R15" s="3">
+        <v>341000</v>
+      </c>
+      <c r="S15" s="3">
         <v>361000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>358000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>341000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>334000</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1196,126 +1221,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>9261000</v>
+      </c>
+      <c r="E17" s="3">
         <v>9121000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10365000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10118000</v>
       </c>
-      <c r="G17" s="3">
-        <v>10110000</v>
-      </c>
       <c r="H17" s="3">
+        <v>10425000</v>
+      </c>
+      <c r="I17" s="3">
         <v>9385000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>11127000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>10988000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>12902000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>12013000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>13466000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2806000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2679000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2827000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2284000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2399000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2406000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2046000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1895000</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>766000</v>
+      </c>
+      <c r="E18" s="3">
         <v>502000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-652000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-160000</v>
       </c>
-      <c r="G18" s="3">
-        <v>174000</v>
-      </c>
       <c r="H18" s="3">
+        <v>-141000</v>
+      </c>
+      <c r="I18" s="3">
         <v>594000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-769000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-288000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1894000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2190000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-3639000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>353000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>508000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>323000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>778000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>393000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>480000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>515000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>646000</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1337,303 +1369,319 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>99000</v>
+      </c>
+      <c r="E20" s="3">
         <v>38000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>92000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>103000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-25000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>124000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>18000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>111000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-89000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-106000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-94000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>476000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-171000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>69000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>99000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>67000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>109000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-25000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2310000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2226000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1000000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1625000</v>
       </c>
-      <c r="G21" s="3">
-        <v>2223000</v>
-      </c>
       <c r="H21" s="3">
+        <v>1908000</v>
+      </c>
+      <c r="I21" s="3">
         <v>2459000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1127000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1659000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4270000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3878000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3649000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2323000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1642000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1952000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1991000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1564000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1785000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1594000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1613000</v>
       </c>
     </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>492000</v>
+      </c>
+      <c r="E22" s="3">
         <v>517000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>522000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>498000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>540000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>550000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>518000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>576000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>558000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>555000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>511000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>153000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>154000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>159000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>157000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>163000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>173000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>171000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>172000</v>
       </c>
     </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-356000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-178000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-10035000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-819000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-613000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-532000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1480000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1238000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2541000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2851000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4244000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>676000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>183000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>233000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>720000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>297000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>416000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>319000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>456000</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>284000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-319000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-7000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>136000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-221000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-125000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-260000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-178000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-462000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-566000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-836000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>201000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>92000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>36000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>106000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>98000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-11000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>156000</v>
       </c>
     </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1691,126 +1739,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-640000</v>
+      </c>
+      <c r="E26" s="3">
         <v>141000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-10028000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-955000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-392000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-407000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1220000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1060000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2079000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2285000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3408000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>475000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>91000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>197000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>718000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>191000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>318000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>330000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>300000</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-490000</v>
+      </c>
+      <c r="E27" s="3">
         <v>135000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-9986000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-970000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-400000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-417000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1240000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1069000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2101000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2308000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3418000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>407000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>48000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>120000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>515000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>106000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>205000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>223000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1868,8 +1925,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1927,8 +1987,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1986,8 +2049,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2045,126 +2111,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-99000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-38000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-92000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-103000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>25000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-124000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-18000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-111000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>89000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>106000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>94000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-476000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>171000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-69000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-99000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-67000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-109000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>25000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-494000</v>
+      </c>
+      <c r="E33" s="3">
         <v>135000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-9986000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-966000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-400000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-417000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1240000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1069000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2101000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2308000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3418000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>407000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>48000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>120000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>515000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>106000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>205000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>223000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2222,131 +2297,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-494000</v>
+      </c>
+      <c r="E35" s="3">
         <v>135000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-9986000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-966000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-400000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-417000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1240000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1069000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2101000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2308000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3418000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>407000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>48000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>120000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>515000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>106000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>205000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>223000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2368,8 +2452,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2391,94 +2476,98 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5312000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3336000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3613000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2976000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3780000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2383000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3027000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2594000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3731000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2422000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2575000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4162000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3905000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3116000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2834000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2008000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2091000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1893000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1683000</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E42" s="3">
         <v>18000</v>
       </c>
-      <c r="E42" s="3">
-        <v>68000</v>
-      </c>
       <c r="F42" s="3">
+        <v>50000</v>
+      </c>
+      <c r="G42" s="3">
         <v>93000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>24000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>83000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>72000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>40000</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -2509,67 +2598,73 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3887000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3498000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3599000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3643000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4532000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3683000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3485000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3558000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6380000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6669000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7049000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2426000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2446000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2462000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2657000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2476000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2537000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2444000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2473000</v>
       </c>
     </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2594,8 +2689,8 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2627,303 +2722,321 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2129000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2140000</v>
       </c>
-      <c r="E45" s="3">
-        <v>2659000</v>
-      </c>
       <c r="F45" s="3">
+        <v>2677000</v>
+      </c>
+      <c r="G45" s="3">
         <v>2742000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2906000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2755000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3607000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3374000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3888000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3581000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5825000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>585000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>913000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1078000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1237000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1381000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1502000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1141000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>561000</v>
       </c>
     </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>14078000</v>
+      </c>
+      <c r="E46" s="3">
         <v>12505000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>13430000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>13902000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>14218000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12831000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>13773000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>13727000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>13999000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12672000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>15449000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7173000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>7264000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6656000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6728000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5865000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6130000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5478000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4717000</v>
       </c>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1098000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1257000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1301000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1437000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1470000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1443000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1491000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1499000</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
-      <c r="N47" s="3" t="s">
+      <c r="M47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P47" s="3">
         <v>543000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>545000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>559000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>522000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>507000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>536000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>530000</v>
       </c>
     </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7214000</v>
+      </c>
+      <c r="E48" s="3">
         <v>6158000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6043000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5937000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7730000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5810000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5473000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5325000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8490000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8365000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8515000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1328000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1336000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1310000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1239000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1189000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1206000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1125000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1088000</v>
       </c>
     </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>78314000</v>
+      </c>
+      <c r="E49" s="3">
         <v>79675000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>80907000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>91978000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>95784000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>97055000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>100888000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>103370000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>106072000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>109482000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>113117000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>22611000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>23061000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>23429000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>23694000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>23765000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>24149000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>24194000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>24618000</v>
       </c>
     </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2981,8 +3094,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3040,67 +3156,73 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3243000</v>
+      </c>
+      <c r="E52" s="3">
         <v>6738000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6348000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6565000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2858000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6610000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6993000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6663000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5440000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5530000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5159000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2687000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2223000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2378000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2352000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2284000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2095000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2105000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2136000</v>
       </c>
     </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3158,67 +3280,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>104560000</v>
+      </c>
+      <c r="E54" s="3">
         <v>106333000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>108029000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>119819000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>122757000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>123749000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>128618000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>130584000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>134001000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>136049000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>142240000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>33799000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>34427000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>34318000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>34572000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>33625000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>34087000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>33438000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>33089000</v>
       </c>
     </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3240,8 +3368,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3263,362 +3392,381 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1055000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1120000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1151000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1245000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1260000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1329000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1689000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1123000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1454000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1534000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1397000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>521000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>412000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2361000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2174000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2128000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>397000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>403000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>367000</v>
       </c>
     </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3162000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3043000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3669000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3430000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2186000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1302000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3001000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3496000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>447000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1338000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1175000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>794000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>397000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>349000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>585000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>351000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>392000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>336000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>339000</v>
       </c>
     </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1569000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1788000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2375000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2312000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1924000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2431000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2020000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2099000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13116000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11804000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11864000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2247000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2650000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>625000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>806000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>663000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2293000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2017000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1870000</v>
       </c>
     </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>15810000</v>
+      </c>
+      <c r="E60" s="3">
         <v>15695000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>17768000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>16956000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>15332000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>14588000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>16906000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>16380000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>15017000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>14676000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>14436000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3562000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3459000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3335000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3565000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3142000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3082000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2756000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2576000</v>
       </c>
     </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>39844000</v>
+      </c>
+      <c r="E61" s="3">
         <v>37166000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>37293000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>39155000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>45104000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>43504000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>44289000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>45435000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>48820000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>48799000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>51594000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>13605000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>14617000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>14436000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>14462000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>14675000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>15253000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>14981000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>14944000</v>
       </c>
     </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6529000</v>
+      </c>
+      <c r="E62" s="3">
         <v>9769000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9532000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9892000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6689000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>10275000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10527000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>10337000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>21497000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>22494000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>23263000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3070000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2955000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3149000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3237000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3233000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3369000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3661000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3769000</v>
       </c>
     </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3676,8 +3824,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3735,8 +3886,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3794,67 +3948,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>69622000</v>
+      </c>
+      <c r="E66" s="3">
         <v>70159000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>72614000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>74525000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>76285000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>77607000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>81833000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>82742000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>86906000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>87532000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>90857000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>21830000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>22828000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>22707000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>23034000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>22810000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>23623000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>23351000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>23222000</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3876,8 +4036,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3935,8 +4096,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3994,8 +4158,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4053,8 +4220,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4112,67 +4282,73 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-12239000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-11745000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-11880000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1894000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-928000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-526000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-105000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1133000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2205000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4306000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6614000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>10033000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9580000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9522000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>9360000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>8682000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>8543000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>8278000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7980000</v>
       </c>
     </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4230,8 +4406,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4289,8 +4468,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4348,67 +4530,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>34037000</v>
+      </c>
+      <c r="E76" s="3">
         <v>35100000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>34345000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>44151000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>45226000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>44774000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>45452000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>46496000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>47095000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>48517000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>51383000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11969000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11599000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11611000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>11538000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>10815000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>10464000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>10087000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>9867000</v>
       </c>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4466,131 +4654,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-494000</v>
+      </c>
+      <c r="E81" s="3">
         <v>135000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-9986000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-966000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-400000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-417000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1240000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1069000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2101000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2308000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3418000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>407000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>48000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>120000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>515000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>106000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>205000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>223000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4612,67 +4809,71 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2024000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1989000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1914000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2058000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2169000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2233000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2266000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>525000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6253000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6174000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>7382000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1494000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1305000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1560000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1114000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1104000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1196000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1104000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>985000</v>
       </c>
     </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4730,8 +4931,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4789,8 +4993,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4848,8 +5055,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4907,8 +5117,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4966,67 +5179,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2715000</v>
+      </c>
+      <c r="E89" s="3">
         <v>847000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1228000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>585000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3578000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2516000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2014000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-631000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2846000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>124000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1011000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>323000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>884000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>811000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>834000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>269000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>553000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>860000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>991000</v>
       </c>
     </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5048,67 +5267,71 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-286000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-215000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-252000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-195000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-268000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-457000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-292000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-299000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-364000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-316000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-222000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-85000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-100000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-106000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-77000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-90000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-112000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-73000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-112000</v>
       </c>
     </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5166,8 +5389,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5225,67 +5451,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-218000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>70000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-207000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-234000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-458000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-310000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-257000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-218000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>862000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>2351000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>529000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-26000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-226000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>40000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>156000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-153000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-396000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-84000</v>
       </c>
     </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5307,8 +5539,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5333,8 +5566,8 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -5366,8 +5599,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5425,8 +5661,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5484,8 +5723,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5543,181 +5785,193 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-600000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-875000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1037000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1237000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1529000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2625000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1251000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-432000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1272000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2313000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3570000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-587000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-42000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-273000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-69000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-469000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-277000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-274000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-739000</v>
       </c>
     </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>74000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-80000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-15000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>29000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>61000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-56000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-61000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-5000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>61000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-56000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-61000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-5000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-37000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-20000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>21000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-70000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>43000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>28000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1926000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-127000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>231000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-933000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1889000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-647000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>438000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1291000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1417000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1383000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-269000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>260000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>779000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>292000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>826000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-114000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>166000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>218000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>204000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WBD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WBD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
   <si>
     <t>WBD</t>
   </si>
@@ -656,281 +656,293 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8979000</v>
+      </c>
+      <c r="E8" s="3">
         <v>10027000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9623000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9713000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9958000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>10284000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9979000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>10358000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>10700000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>11008000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9823000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>9827000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3159000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3187000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3150000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3062000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2792000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2886000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2561000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2541000</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>5096000</v>
+      </c>
+      <c r="E9" s="3">
         <v>5457000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5036000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6204000</v>
       </c>
-      <c r="G9" s="3">
-        <v>6058000</v>
-      </c>
       <c r="H9" s="3">
+        <v>5932000</v>
+      </c>
+      <c r="I9" s="3">
         <v>6000000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5118000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6636000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6589000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6954000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4718000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6123000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1232000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1065000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1527000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1054000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>969000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1089000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1002000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>804000</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3883000</v>
+      </c>
+      <c r="E10" s="3">
         <v>4570000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4587000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3509000</v>
       </c>
-      <c r="G10" s="3">
-        <v>3900000</v>
-      </c>
       <c r="H10" s="3">
+        <v>4026000</v>
+      </c>
+      <c r="I10" s="3">
         <v>4284000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4861000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3722000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4111000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4054000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5105000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3704000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1927000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2122000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1623000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2008000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1823000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1797000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1559000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1737000</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -953,8 +965,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1015,8 +1028,11 @@
       <c r="V12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1077,132 +1093,141 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>263000</v>
+      </c>
+      <c r="E14" s="3">
         <v>569000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>174000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>8832000</v>
       </c>
-      <c r="G14" s="3">
-        <v>118000</v>
-      </c>
       <c r="H14" s="3">
+        <v>244000</v>
+      </c>
+      <c r="I14" s="3">
         <v>8000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>495000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>215000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>308000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1198000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2430000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1535000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>9000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>5000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>15000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>8000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>18000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>150000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>70000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>122000</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1547000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1643000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1762000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1744000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1888000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2024000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1989000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1914000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2058000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2169000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2233000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2266000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>525000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>539000</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>341000</v>
       </c>
       <c r="R15" s="3">
         <v>341000</v>
       </c>
       <c r="S15" s="3">
+        <v>341000</v>
+      </c>
+      <c r="T15" s="3">
         <v>361000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>358000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>341000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>334000</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1222,132 +1247,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8758000</v>
+      </c>
+      <c r="E17" s="3">
         <v>9261000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>9121000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10365000</v>
       </c>
-      <c r="G17" s="3">
-        <v>10118000</v>
-      </c>
       <c r="H17" s="3">
+        <v>9992000</v>
+      </c>
+      <c r="I17" s="3">
         <v>10425000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9385000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>11127000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10988000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>12902000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>12013000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>13466000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2806000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2679000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2827000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2284000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2399000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2406000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2046000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1895000</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>221000</v>
+      </c>
+      <c r="E18" s="3">
         <v>766000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>502000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-652000</v>
       </c>
-      <c r="G18" s="3">
-        <v>-160000</v>
-      </c>
       <c r="H18" s="3">
+        <v>-34000</v>
+      </c>
+      <c r="I18" s="3">
         <v>-141000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>594000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-769000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-288000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1894000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2190000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3639000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>353000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>508000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>323000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>778000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>393000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>480000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>515000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>646000</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1370,318 +1402,334 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E20" s="3">
         <v>99000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>38000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>92000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>103000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-25000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>124000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>18000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>111000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-89000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-106000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-94000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>476000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-171000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>69000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>99000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>67000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>109000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-25000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1782000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2310000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2226000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1000000</v>
       </c>
-      <c r="G21" s="3">
-        <v>1625000</v>
-      </c>
       <c r="H21" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="I21" s="3">
         <v>1908000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2459000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1127000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1659000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4270000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3878000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3649000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2323000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1642000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1952000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1991000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1564000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1785000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1594000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1613000</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>470000</v>
+      </c>
+      <c r="E22" s="3">
         <v>492000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>517000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>522000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>498000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>540000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>550000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>518000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>576000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>558000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>555000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>511000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>153000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>154000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>159000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>157000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>163000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>173000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>171000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>172000</v>
       </c>
     </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-434000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-356000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-178000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-10035000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-819000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-613000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-532000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1480000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1238000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2541000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2851000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4244000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>676000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>183000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>233000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>720000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>297000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>416000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>319000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>456000</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E24" s="3">
         <v>284000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-319000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-7000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>136000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-221000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-125000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-260000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-178000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-462000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-566000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-836000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>201000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>92000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>36000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>106000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>98000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-11000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>156000</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1742,132 +1790,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-449000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-640000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>141000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-10028000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-955000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-392000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-407000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1220000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1060000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2079000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2285000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3408000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>475000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>91000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>197000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>718000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>191000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>318000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>330000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>300000</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-453000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-490000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>135000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-9986000</v>
       </c>
-      <c r="G27" s="3">
-        <v>-970000</v>
-      </c>
       <c r="H27" s="3">
+        <v>-966000</v>
+      </c>
+      <c r="I27" s="3">
         <v>-400000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-417000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1240000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1069000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2101000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2308000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3418000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>407000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>48000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>120000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>515000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>106000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>205000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>223000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1928,8 +1985,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1990,8 +2050,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2052,8 +2115,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2114,132 +2180,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-99000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-38000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-92000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-103000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>25000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-124000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-18000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-111000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>89000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>106000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>94000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-476000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>171000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-69000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-99000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-67000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-109000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>25000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-453000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-494000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>135000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-9986000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-966000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-400000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-417000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1240000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1069000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2101000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2308000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3418000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>407000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>48000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>120000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>515000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>106000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>205000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>223000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2300,137 +2375,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-453000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-494000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>135000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-9986000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-966000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-400000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-417000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1240000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1069000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2101000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2308000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3418000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>407000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>48000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>120000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>515000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>106000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>205000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>223000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2453,8 +2537,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2477,100 +2562,104 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3868000</v>
+      </c>
+      <c r="E41" s="3">
         <v>5312000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3336000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3613000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2976000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3780000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2383000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3027000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2594000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3731000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2422000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2575000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4162000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3905000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3116000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2834000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2008000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2091000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1893000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1683000</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E42" s="3">
         <v>17000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>18000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>50000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>93000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>24000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>83000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>72000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>40000</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -2601,70 +2690,76 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2818000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3887000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3498000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3599000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3643000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4532000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3683000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3485000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3558000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6380000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6669000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7049000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2426000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2446000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2462000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2657000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2476000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2537000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2444000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2473000</v>
       </c>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2692,8 +2787,8 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2725,318 +2820,336 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1909000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2129000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2140000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2677000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2742000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2906000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2755000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3607000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3374000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3888000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3581000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5825000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>585000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>913000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1078000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1237000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1381000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1502000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1141000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>561000</v>
       </c>
     </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12782000</v>
+      </c>
+      <c r="E46" s="3">
         <v>14078000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12505000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>13430000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>13902000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>14218000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12831000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>13773000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>13727000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>13999000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12672000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>15449000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>7173000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>7264000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6656000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6728000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5865000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6130000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5478000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4717000</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1310000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1098000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1257000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1301000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1437000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1470000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1443000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1491000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1499000</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
-      </c>
-      <c r="O47" s="3" t="s">
+      <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q47" s="3">
         <v>543000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>545000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>559000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>522000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>507000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>536000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>530000</v>
       </c>
     </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6211000</v>
+      </c>
+      <c r="E48" s="3">
         <v>7214000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6158000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6043000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5937000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7730000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5810000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5473000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5325000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8490000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8365000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8515000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1328000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1336000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1310000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1239000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1189000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1206000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1125000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1088000</v>
       </c>
     </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>75600000</v>
+      </c>
+      <c r="E49" s="3">
         <v>78314000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>79675000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>80907000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>91978000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>95784000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>97055000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>100888000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>103370000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>106072000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>109482000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>113117000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>22611000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>23061000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>23429000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>23694000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>23765000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>24149000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>24194000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>24618000</v>
       </c>
     </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3097,8 +3210,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3159,70 +3275,76 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5776000</v>
+      </c>
+      <c r="E52" s="3">
         <v>3243000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6738000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6348000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>6565000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2858000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6610000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6993000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6663000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5440000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5530000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5159000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2687000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2223000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2378000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2352000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2284000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2095000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2105000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2136000</v>
       </c>
     </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3283,70 +3405,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>101679000</v>
+      </c>
+      <c r="E54" s="3">
         <v>104560000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>106333000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>108029000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>119819000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>122757000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>123749000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>128618000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>130584000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>134001000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>136049000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>142240000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>33799000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>34427000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>34318000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>34572000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>33625000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>34087000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>33438000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>33089000</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3369,8 +3497,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3393,380 +3522,399 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1008000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1055000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1120000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1151000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1245000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1260000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1329000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1689000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1123000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1454000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1534000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1397000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>521000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>412000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2361000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2174000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2128000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>397000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>403000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>367000</v>
       </c>
     </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2779000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3162000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3043000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3669000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3430000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2186000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1302000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3001000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3496000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>447000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1338000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1175000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>794000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>397000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>349000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>585000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>351000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>392000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>336000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>339000</v>
       </c>
     </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1600000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1569000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1788000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2375000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2312000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1924000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2431000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2020000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2099000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13116000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11804000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11864000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2247000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2650000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>625000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>806000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>663000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2293000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2017000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1870000</v>
       </c>
     </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>15286000</v>
+      </c>
+      <c r="E60" s="3">
         <v>15810000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>15695000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>17768000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>16956000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>15332000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>14588000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>16906000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>16380000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>15017000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>14676000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>14436000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3562000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3459000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3335000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3565000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3142000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3082000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2756000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2576000</v>
       </c>
     </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>34647000</v>
+      </c>
+      <c r="E61" s="3">
         <v>39844000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>37166000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>37293000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>39155000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>45104000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>43504000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>44289000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>45435000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>48820000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>48799000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>51594000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>13605000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>14617000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>14436000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>14462000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>14675000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>15253000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>14981000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>14944000</v>
       </c>
     </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>9012000</v>
+      </c>
+      <c r="E62" s="3">
         <v>6529000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9769000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9532000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>9892000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6689000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10275000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>10527000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10337000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>21497000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>22494000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>23263000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3070000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2955000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3149000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3237000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3233000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3369000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3661000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3769000</v>
       </c>
     </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3827,8 +3975,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3889,8 +4040,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3951,70 +4105,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>66508000</v>
+      </c>
+      <c r="E66" s="3">
         <v>69622000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>70159000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>72614000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>74525000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>76285000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>77607000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>81833000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>82742000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>86906000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>87532000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>90857000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>21830000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>22828000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>22707000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>23034000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>22810000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>23623000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>23351000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>23222000</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4037,8 +4197,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4099,8 +4260,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4161,8 +4325,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4223,8 +4390,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4285,70 +4455,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-12692000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-12239000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-11745000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-11880000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1894000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-928000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-526000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-105000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1133000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2205000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4306000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6614000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>10033000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9580000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>9522000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>9360000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>8682000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>8543000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>8278000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>7980000</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4409,8 +4585,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4471,8 +4650,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4533,70 +4715,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>33836000</v>
+      </c>
+      <c r="E76" s="3">
         <v>34037000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>35100000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>34345000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>44151000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>45226000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>44774000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>45452000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>46496000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>47095000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>48517000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>51383000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11969000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11599000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>11611000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>11538000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>10815000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>10464000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>10087000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9867000</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4657,137 +4845,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-453000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-494000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>135000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-9986000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-966000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-400000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-417000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1240000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1069000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2101000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2308000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3418000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>407000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>48000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>120000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>515000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>106000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>205000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>223000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4810,70 +5007,74 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1888000</v>
+      </c>
+      <c r="E83" s="3">
         <v>2024000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1989000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1914000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2058000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2169000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2233000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2266000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>525000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6253000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6174000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>7382000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1494000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1305000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1560000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1114000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1104000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1196000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1104000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>985000</v>
       </c>
     </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4934,8 +5135,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4996,8 +5200,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5058,8 +5265,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5120,8 +5330,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5182,70 +5395,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>553000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2715000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>847000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1228000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>585000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3578000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2516000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2014000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-631000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2846000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>124000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1011000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>323000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>884000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>811000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>834000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>269000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>553000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>860000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>991000</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5268,70 +5487,74 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-251000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-286000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-215000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-252000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-195000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-268000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-457000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-292000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-299000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-364000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-316000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-222000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-85000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-100000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-106000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-77000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-90000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-112000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-73000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-112000</v>
       </c>
     </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5392,8 +5615,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5454,70 +5680,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-195000</v>
+      </c>
+      <c r="E94" s="3">
         <v>6000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-218000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>70000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-207000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-234000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-458000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-310000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-257000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-218000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>862000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>2351000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>529000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-26000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-226000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>40000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>156000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-153000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-396000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-84000</v>
       </c>
     </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5540,8 +5772,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5569,8 +5802,8 @@
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5602,8 +5835,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5664,8 +5900,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5726,8 +5965,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5788,190 +6030,202 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1895000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-600000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-875000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1037000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1237000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1529000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2625000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1251000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-432000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1272000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2313000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3570000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-587000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-42000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-273000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-69000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-469000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-277000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-274000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-739000</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-74000</v>
+      </c>
+      <c r="E101" s="3">
         <v>74000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-80000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-15000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>29000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>61000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-56000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-61000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-5000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>61000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-56000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-61000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-5000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-37000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-20000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>21000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-70000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>43000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>28000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1442000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1926000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-127000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>231000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-933000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1889000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-647000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>438000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1291000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1417000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1383000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-269000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>260000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>779000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>292000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>826000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-114000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>166000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>218000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>204000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WBD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WBD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
   <si>
     <t>WBD</t>
   </si>
@@ -656,293 +656,305 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>9812000</v>
+      </c>
+      <c r="E8" s="3">
         <v>8979000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>10027000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9623000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9713000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9958000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>10284000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9979000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>10358000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>10700000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>11008000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>9823000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>9827000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3159000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3187000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3150000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3062000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2792000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2886000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2561000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2541000</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>5967000</v>
+      </c>
+      <c r="E9" s="3">
         <v>5096000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5457000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5036000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6204000</v>
       </c>
-      <c r="H9" s="3">
-        <v>5932000</v>
-      </c>
       <c r="I9" s="3">
+        <v>6058000</v>
+      </c>
+      <c r="J9" s="3">
         <v>6000000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5118000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6636000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6589000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6954000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4718000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6123000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1232000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1065000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1527000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1054000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>969000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1089000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1002000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>804000</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3845000</v>
+      </c>
+      <c r="E10" s="3">
         <v>3883000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4570000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4587000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3509000</v>
       </c>
-      <c r="H10" s="3">
-        <v>4026000</v>
-      </c>
       <c r="I10" s="3">
+        <v>3900000</v>
+      </c>
+      <c r="J10" s="3">
         <v>4284000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4861000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3722000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4111000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4054000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5105000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3704000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1927000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2122000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1623000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2008000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1823000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1797000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1559000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1737000</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -966,8 +978,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1031,8 +1044,11 @@
       <c r="W12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1096,138 +1112,147 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-2835000</v>
+      </c>
+      <c r="E14" s="3">
         <v>263000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>569000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>174000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>8832000</v>
       </c>
-      <c r="H14" s="3">
-        <v>244000</v>
-      </c>
       <c r="I14" s="3">
+        <v>118000</v>
+      </c>
+      <c r="J14" s="3">
         <v>8000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>495000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>215000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>308000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1198000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2430000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1535000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>9000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>5000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>15000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>8000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>18000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>150000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>70000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>122000</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1447000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1547000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1643000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1762000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1744000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1888000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2024000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1989000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1914000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2058000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2169000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2233000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2266000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>525000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>539000</v>
-      </c>
-      <c r="R15" s="3">
-        <v>341000</v>
       </c>
       <c r="S15" s="3">
         <v>341000</v>
       </c>
       <c r="T15" s="3">
+        <v>341000</v>
+      </c>
+      <c r="U15" s="3">
         <v>361000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>358000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>341000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>334000</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1248,138 +1273,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>9871000</v>
+      </c>
+      <c r="E17" s="3">
         <v>8758000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>9261000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9121000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>10365000</v>
       </c>
-      <c r="H17" s="3">
-        <v>9992000</v>
-      </c>
       <c r="I17" s="3">
+        <v>10118000</v>
+      </c>
+      <c r="J17" s="3">
         <v>10425000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>9385000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11127000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10988000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>12902000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>12013000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>13466000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2806000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2679000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2827000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2284000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2399000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2406000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2046000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1895000</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-59000</v>
+      </c>
+      <c r="E18" s="3">
         <v>221000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>766000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>502000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-652000</v>
       </c>
-      <c r="H18" s="3">
-        <v>-34000</v>
-      </c>
       <c r="I18" s="3">
+        <v>-160000</v>
+      </c>
+      <c r="J18" s="3">
         <v>-141000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>594000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-769000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-288000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1894000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2190000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3639000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>353000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>508000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>323000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>778000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>393000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>480000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>515000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>646000</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1403,333 +1435,349 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-88000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-14000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>99000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>38000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>92000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>103000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-25000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>124000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>18000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>111000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-89000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-106000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-94000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>476000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-171000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>69000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>99000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>67000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>109000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-25000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1476000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1782000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2310000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2226000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1000000</v>
       </c>
-      <c r="H21" s="3">
-        <v>1751000</v>
-      </c>
       <c r="I21" s="3">
+        <v>1625000</v>
+      </c>
+      <c r="J21" s="3">
         <v>1908000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2459000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1127000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1659000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4270000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3878000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3649000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2323000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1642000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1952000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1991000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1564000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1785000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1594000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1613000</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>469000</v>
+      </c>
+      <c r="E22" s="3">
         <v>470000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>492000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>517000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>522000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>498000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>540000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>550000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>518000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>576000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>558000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>555000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>511000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>153000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>154000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>159000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>157000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>163000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>173000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>171000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>172000</v>
       </c>
     </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2454000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-434000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-356000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-178000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10035000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-819000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-613000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-532000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1480000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1238000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2541000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2851000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4244000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>676000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>183000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>233000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>720000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>297000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>416000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>319000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>456000</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>866000</v>
+      </c>
+      <c r="E24" s="3">
         <v>15000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>284000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-319000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-7000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>136000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-221000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-125000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-260000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-178000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-462000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-566000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-836000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>201000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>92000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>36000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>106000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>98000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-11000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>156000</v>
       </c>
     </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1793,138 +1841,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1588000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-449000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-640000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>141000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-10028000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-955000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-392000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-407000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1220000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1060000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2079000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2285000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3408000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>475000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>91000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>197000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>718000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>191000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>318000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>330000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>300000</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1580000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-453000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-490000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>135000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-9986000</v>
       </c>
-      <c r="H27" s="3">
-        <v>-966000</v>
-      </c>
       <c r="I27" s="3">
+        <v>-970000</v>
+      </c>
+      <c r="J27" s="3">
         <v>-400000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-417000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1240000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1069000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2101000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2308000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3418000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>407000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>48000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>120000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>515000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>106000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>205000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>223000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1988,8 +2045,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2053,8 +2113,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2118,8 +2181,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2183,138 +2249,147 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>88000</v>
+      </c>
+      <c r="E32" s="3">
         <v>14000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-99000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-38000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-92000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-103000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>25000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-124000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-18000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-111000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>89000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>106000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>94000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-476000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>171000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-69000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-99000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-67000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-109000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>25000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1580000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-453000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-494000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>135000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-9986000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-966000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-400000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-417000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1240000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1069000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2101000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2308000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3418000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>407000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>48000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>120000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>515000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>106000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>205000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>223000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2378,143 +2453,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1580000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-453000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-494000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>135000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-9986000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-966000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-400000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-417000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1240000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1069000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2101000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2308000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3418000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>407000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>48000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>120000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>515000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>106000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>205000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>223000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2538,8 +2622,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2563,106 +2648,110 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4888000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3868000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5312000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3336000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3613000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2976000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3780000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2383000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3027000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2594000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3731000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2422000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2575000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4162000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3905000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3116000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2834000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2008000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2091000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1893000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1683000</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E42" s="3">
         <v>36000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>17000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>18000</v>
       </c>
-      <c r="G42" s="3">
-        <v>50000</v>
-      </c>
       <c r="H42" s="3">
+        <v>68000</v>
+      </c>
+      <c r="I42" s="3">
         <v>93000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>24000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>83000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>72000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>40000</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -2693,73 +2782,79 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3210000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2818000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3887000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3498000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3599000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3643000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4532000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3683000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3485000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3558000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6380000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6669000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7049000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2426000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2446000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2462000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2657000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2476000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2537000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2444000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2473000</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2790,8 +2885,8 @@
       <c r="L44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2823,333 +2918,351 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2251000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1909000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2129000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2140000</v>
       </c>
-      <c r="G45" s="3">
-        <v>2677000</v>
-      </c>
       <c r="H45" s="3">
+        <v>2659000</v>
+      </c>
+      <c r="I45" s="3">
         <v>2742000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2906000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2755000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3607000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3374000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3888000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3581000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5825000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>585000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>913000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1078000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1237000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1381000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1502000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1141000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>561000</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13611000</v>
+      </c>
+      <c r="E46" s="3">
         <v>12782000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>14078000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12505000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>13430000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>13902000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>14218000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>12831000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>13773000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>13727000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>13999000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12672000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>15449000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>7173000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>7264000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6656000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6728000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5865000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6130000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5478000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4717000</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1310000</v>
+        <v>1262000</v>
       </c>
       <c r="E47" s="3">
+        <v>1293000</v>
+      </c>
+      <c r="F47" s="3">
         <v>1098000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1257000</v>
       </c>
-      <c r="G47" s="3">
-        <v>1301000</v>
-      </c>
       <c r="H47" s="3">
+        <v>1517000</v>
+      </c>
+      <c r="I47" s="3">
         <v>1437000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1470000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1443000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1491000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1499000</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3" t="s">
+      <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R47" s="3">
         <v>543000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>545000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>559000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>522000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>507000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>536000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>530000</v>
       </c>
     </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6413000</v>
+      </c>
+      <c r="E48" s="3">
         <v>6211000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7214000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6158000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6043000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5937000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7730000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5810000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5473000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5325000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8490000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8365000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8515000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1328000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1336000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1310000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1239000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1189000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1206000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1125000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1088000</v>
       </c>
     </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>74662000</v>
+      </c>
+      <c r="E49" s="3">
         <v>75600000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>78314000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>79675000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>80907000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>91978000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>95784000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>97055000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>100888000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>103370000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>106072000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>109482000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>113117000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>22611000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>23061000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>23429000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>23694000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>23765000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>24149000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>24194000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>24618000</v>
       </c>
     </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3213,8 +3326,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3278,73 +3394,79 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>5776000</v>
+        <v>5779000</v>
       </c>
       <c r="E52" s="3">
+        <v>5793000</v>
+      </c>
+      <c r="F52" s="3">
         <v>3243000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6738000</v>
       </c>
-      <c r="G52" s="3">
-        <v>6348000</v>
-      </c>
       <c r="H52" s="3">
+        <v>6132000</v>
+      </c>
+      <c r="I52" s="3">
         <v>6565000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2858000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6610000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6993000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6663000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5440000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5530000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5159000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2687000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2223000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2378000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2352000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2284000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2095000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2105000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2136000</v>
       </c>
     </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3408,73 +3530,79 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>101727000</v>
+      </c>
+      <c r="E54" s="3">
         <v>101679000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>104560000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>106333000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>108029000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>119819000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>122757000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>123749000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>128618000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>130584000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>134001000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>136049000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>142240000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>33799000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>34427000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>34318000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>34572000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>33625000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>34087000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>33438000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>33089000</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3498,8 +3626,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3523,398 +3652,417 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1074000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1008000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1055000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1120000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1151000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1245000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1260000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1329000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1689000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1123000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1454000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1534000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1397000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>521000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>412000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2361000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2174000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2128000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>397000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>403000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>367000</v>
       </c>
     </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>221000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2779000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3162000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3043000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3669000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3430000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2186000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1302000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3001000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3496000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>447000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1338000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1175000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>794000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>397000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>349000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>585000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>351000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>392000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>336000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>339000</v>
       </c>
     </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1527000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1600000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1569000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1788000</v>
       </c>
-      <c r="G59" s="3">
-        <v>2375000</v>
-      </c>
       <c r="H59" s="3">
+        <v>2022000</v>
+      </c>
+      <c r="I59" s="3">
         <v>2312000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1924000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2431000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2020000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2099000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13116000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11804000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11864000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2247000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2650000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>625000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>806000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>663000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2293000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2017000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1870000</v>
       </c>
     </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>13040000</v>
+      </c>
+      <c r="E60" s="3">
         <v>15286000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>15810000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>15695000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>17768000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>16956000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>15332000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>14588000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>16906000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>16380000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>15017000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>14676000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>14436000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3562000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3459000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3335000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3565000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3142000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3082000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2756000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2576000</v>
       </c>
     </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>34411000</v>
+      </c>
+      <c r="E61" s="3">
         <v>34647000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>39844000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>37166000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>37293000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>39155000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>45104000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>43504000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>44289000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>45435000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>48820000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>48799000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>51594000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>13605000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>14617000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>14436000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>14462000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>14675000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>15253000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>14981000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>14944000</v>
       </c>
     </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>9012000</v>
+        <v>10205000</v>
       </c>
       <c r="E62" s="3">
+        <v>9651000</v>
+      </c>
+      <c r="F62" s="3">
         <v>6529000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9769000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>9532000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9892000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6689000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>10275000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10527000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>10337000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>21497000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>22494000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>23263000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3070000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2955000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3149000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3237000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3233000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3369000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3661000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3769000</v>
       </c>
     </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3978,8 +4126,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4043,8 +4194,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4108,73 +4262,79 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>64381000</v>
+      </c>
+      <c r="E66" s="3">
         <v>66508000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>69622000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>70159000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>72614000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>74525000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>76285000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>77607000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>81833000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>82742000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>86906000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>87532000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>90857000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>21830000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>22828000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>22707000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>23034000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>22810000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>23623000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>23351000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>23222000</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4198,8 +4358,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4263,8 +4424,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4328,8 +4492,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4393,8 +4560,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4458,73 +4628,79 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-11112000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-12692000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-12239000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-11745000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-11880000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1894000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-928000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-526000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-105000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1133000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2205000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4306000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6614000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>10033000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>9580000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>9522000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>9360000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>8682000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>8543000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>8278000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>7980000</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4588,8 +4764,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4653,8 +4832,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4718,73 +4900,79 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>36049000</v>
+      </c>
+      <c r="E76" s="3">
         <v>33836000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>34037000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>35100000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>34345000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>44151000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>45226000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>44774000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>45452000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>46496000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>47095000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>48517000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>51383000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11969000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>11599000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>11611000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>11538000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>10815000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>10464000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>10087000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>9867000</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4848,143 +5036,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1580000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-453000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-494000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>135000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-9986000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-966000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-400000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-417000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1240000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1069000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2101000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2308000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3418000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>407000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>48000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>120000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>515000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>106000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>205000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>223000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5008,73 +5205,77 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1744000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1888000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2024000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1989000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1914000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2058000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2169000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2233000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2266000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>525000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6253000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>6174000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>7382000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1494000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1305000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1560000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1114000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1104000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1196000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1104000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>985000</v>
       </c>
     </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5138,8 +5339,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5203,8 +5407,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5268,8 +5475,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5333,8 +5543,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5398,73 +5611,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>983000</v>
+      </c>
+      <c r="E89" s="3">
         <v>553000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2715000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>847000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1228000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>585000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3578000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2516000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2014000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-631000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2846000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>124000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1011000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>323000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>884000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>811000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>834000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>269000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>553000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>860000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>991000</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5488,73 +5707,77 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-281000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-251000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-286000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-215000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-252000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-195000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-268000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-457000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-292000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-299000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-364000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-316000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-222000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-85000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-100000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-106000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-77000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-90000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-112000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-73000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-112000</v>
       </c>
     </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5618,8 +5841,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5683,73 +5909,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-236000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-195000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>6000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-218000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>70000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-207000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-234000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-458000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-310000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-257000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-218000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>862000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>2351000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>529000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-26000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-226000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>40000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>156000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-153000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-396000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-84000</v>
       </c>
     </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5773,8 +6005,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5805,8 +6038,8 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -5838,8 +6071,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5903,8 +6139,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5968,8 +6207,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6033,199 +6275,211 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1895000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-600000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-875000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1037000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1237000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1529000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2625000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1251000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-432000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1272000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2313000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3570000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-587000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-42000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-273000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-69000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-469000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-277000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-274000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-739000</v>
       </c>
     </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-74000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>74000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-80000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-15000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>29000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>61000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-56000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-61000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-5000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>61000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-56000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-61000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-37000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-20000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>21000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-70000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>43000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>28000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>917000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1442000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1926000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-127000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>231000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-933000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1889000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-647000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>438000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1291000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1417000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1383000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-269000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>260000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>779000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>292000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>826000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-114000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>166000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>218000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>204000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WBD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WBD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
   <si>
     <t>WBD</t>
   </si>
@@ -656,317 +656,329 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>9460000</v>
+      </c>
+      <c r="E8" s="3">
         <v>9045000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9812000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8979000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>10027000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9623000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9713000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9958000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>10284000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9979000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>10358000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10700000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>11008000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>9823000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>9827000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3159000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3187000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3150000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3062000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2792000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2886000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2561000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2541000</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>5119000</v>
+      </c>
+      <c r="E9" s="3">
         <v>4528000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5967000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5096000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5457000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5036000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6204000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6058000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6000000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5118000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6636000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6589000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6954000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4718000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6123000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1232000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1065000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1527000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1054000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>969000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1089000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1002000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>804000</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4341000</v>
+      </c>
+      <c r="E10" s="3">
         <v>4517000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3845000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3883000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4570000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4587000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3509000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3900000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4284000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4861000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3722000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4111000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4054000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5105000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3704000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1927000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2122000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1623000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2008000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1823000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1797000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1559000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1737000</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -992,8 +1004,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1063,8 +1076,11 @@
       <c r="Y12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1134,150 +1150,159 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>355000</v>
+      </c>
+      <c r="E14" s="3">
         <v>178000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-2835000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>263000</v>
       </c>
-      <c r="G14" s="3">
-        <v>569000</v>
-      </c>
       <c r="H14" s="3">
+        <v>489000</v>
+      </c>
+      <c r="I14" s="3">
         <v>174000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>8832000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>118000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>8000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>495000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>215000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>308000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1198000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2430000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1535000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>9000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>5000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>15000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>8000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>18000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>150000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>70000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>122000</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1315000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1375000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1447000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1547000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1643000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1762000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1744000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1888000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2024000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1989000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1914000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2058000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2169000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2233000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2266000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>525000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>539000</v>
-      </c>
-      <c r="T15" s="3">
-        <v>341000</v>
       </c>
       <c r="U15" s="3">
         <v>341000</v>
       </c>
       <c r="V15" s="3">
+        <v>341000</v>
+      </c>
+      <c r="W15" s="3">
         <v>361000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>358000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>341000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>334000</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1300,150 +1325,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8762000</v>
+      </c>
+      <c r="E17" s="3">
         <v>8255000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>9871000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8758000</v>
       </c>
-      <c r="G17" s="3">
-        <v>9261000</v>
-      </c>
       <c r="H17" s="3">
+        <v>9385000</v>
+      </c>
+      <c r="I17" s="3">
         <v>9121000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>10365000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>10118000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10425000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9385000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>11127000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>10988000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>12902000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>12013000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>13466000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2806000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2679000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2827000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2284000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2399000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2406000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2046000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1895000</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>698000</v>
+      </c>
+      <c r="E18" s="3">
         <v>790000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-59000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>221000</v>
       </c>
-      <c r="G18" s="3">
-        <v>766000</v>
-      </c>
       <c r="H18" s="3">
+        <v>642000</v>
+      </c>
+      <c r="I18" s="3">
         <v>502000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-652000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-160000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-141000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>594000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-769000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-288000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1894000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2190000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-3639000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>353000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>508000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>323000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>778000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>393000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>480000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>515000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>646000</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1469,363 +1501,379 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>66000</v>
+        <v>200000</v>
       </c>
       <c r="E20" s="3">
+        <v>62000</v>
+      </c>
+      <c r="F20" s="3">
         <v>-88000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-14000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
+        <v>135000</v>
+      </c>
+      <c r="I20" s="3">
+        <v>26000</v>
+      </c>
+      <c r="J20" s="3">
+        <v>92000</v>
+      </c>
+      <c r="K20" s="3">
+        <v>103000</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="M20" s="3">
+        <v>124000</v>
+      </c>
+      <c r="N20" s="3">
+        <v>18000</v>
+      </c>
+      <c r="O20" s="3">
+        <v>111000</v>
+      </c>
+      <c r="P20" s="3">
+        <v>-89000</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>-106000</v>
+      </c>
+      <c r="R20" s="3">
+        <v>-94000</v>
+      </c>
+      <c r="S20" s="3">
+        <v>476000</v>
+      </c>
+      <c r="T20" s="3">
+        <v>-171000</v>
+      </c>
+      <c r="U20" s="3">
+        <v>69000</v>
+      </c>
+      <c r="V20" s="3">
         <v>99000</v>
       </c>
-      <c r="H20" s="3">
-        <v>38000</v>
-      </c>
-      <c r="I20" s="3">
-        <v>92000</v>
-      </c>
-      <c r="J20" s="3">
-        <v>103000</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="W20" s="3">
+        <v>67000</v>
+      </c>
+      <c r="X20" s="3">
+        <v>109000</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-25000</v>
       </c>
-      <c r="L20" s="3">
-        <v>124000</v>
-      </c>
-      <c r="M20" s="3">
-        <v>18000</v>
-      </c>
-      <c r="N20" s="3">
-        <v>111000</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-89000</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-106000</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-94000</v>
-      </c>
-      <c r="R20" s="3">
-        <v>476000</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-171000</v>
-      </c>
-      <c r="T20" s="3">
-        <v>69000</v>
-      </c>
-      <c r="U20" s="3">
-        <v>99000</v>
-      </c>
-      <c r="V20" s="3">
-        <v>67000</v>
-      </c>
-      <c r="W20" s="3">
-        <v>109000</v>
-      </c>
-      <c r="X20" s="3">
-        <v>-25000</v>
-      </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2099000</v>
+        <v>1813000</v>
       </c>
       <c r="E21" s="3">
+        <v>2103000</v>
+      </c>
+      <c r="F21" s="3">
         <v>1476000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1782000</v>
       </c>
-      <c r="G21" s="3">
-        <v>2310000</v>
-      </c>
       <c r="H21" s="3">
-        <v>2226000</v>
+        <v>2150000</v>
       </c>
       <c r="I21" s="3">
+        <v>2238000</v>
+      </c>
+      <c r="J21" s="3">
         <v>1000000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1625000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1908000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2459000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1127000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1659000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4270000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3878000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3649000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2323000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1642000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1952000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1991000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1564000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1785000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1594000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1613000</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>566000</v>
+        <v>587000</v>
       </c>
       <c r="E22" s="3">
+        <v>570000</v>
+      </c>
+      <c r="F22" s="3">
         <v>469000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>470000</v>
       </c>
-      <c r="G22" s="3">
-        <v>492000</v>
-      </c>
       <c r="H22" s="3">
-        <v>517000</v>
+        <v>412000</v>
       </c>
       <c r="I22" s="3">
+        <v>529000</v>
+      </c>
+      <c r="J22" s="3">
         <v>522000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>498000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>540000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>550000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>518000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>576000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>558000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>555000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>511000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>153000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>154000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>159000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>157000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>163000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>173000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>171000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>172000</v>
       </c>
     </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-408000</v>
+      </c>
+      <c r="E23" s="3">
         <v>27000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2454000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-434000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-356000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-178000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-10035000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-819000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-613000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-532000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1480000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1238000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2541000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2851000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4244000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>676000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>183000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>233000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>720000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>297000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>416000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>319000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>456000</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-161000</v>
+      </c>
+      <c r="E24" s="3">
         <v>170000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>866000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>15000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>284000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-319000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-7000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>136000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-221000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-125000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-260000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-178000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-462000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-566000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-836000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>201000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>92000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>36000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>106000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>98000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>156000</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1895,150 +1943,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-247000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-143000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1588000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-449000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-640000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>141000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-10028000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-955000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-392000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-407000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1220000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1060000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2079000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2285000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3408000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>475000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>91000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>197000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>718000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>191000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>318000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>330000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>300000</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-251000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-148000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1580000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-453000</v>
       </c>
-      <c r="G27" s="3">
-        <v>-490000</v>
-      </c>
       <c r="H27" s="3">
+        <v>-493000</v>
+      </c>
+      <c r="I27" s="3">
         <v>135000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-9986000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-970000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-400000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-417000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1240000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1069000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2101000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2308000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3418000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>407000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>48000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>120000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>515000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>106000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>205000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>223000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2108,8 +2165,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2179,8 +2239,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2250,8 +2313,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2321,150 +2387,159 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-66000</v>
+        <v>-200000</v>
       </c>
       <c r="E32" s="3">
+        <v>-62000</v>
+      </c>
+      <c r="F32" s="3">
         <v>88000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>14000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
+        <v>-135000</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-92000</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-103000</v>
+      </c>
+      <c r="L32" s="3">
+        <v>25000</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-124000</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="O32" s="3">
+        <v>-111000</v>
+      </c>
+      <c r="P32" s="3">
+        <v>89000</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>106000</v>
+      </c>
+      <c r="R32" s="3">
+        <v>94000</v>
+      </c>
+      <c r="S32" s="3">
+        <v>-476000</v>
+      </c>
+      <c r="T32" s="3">
+        <v>171000</v>
+      </c>
+      <c r="U32" s="3">
+        <v>-69000</v>
+      </c>
+      <c r="V32" s="3">
         <v>-99000</v>
       </c>
-      <c r="H32" s="3">
-        <v>-38000</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-92000</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-103000</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="W32" s="3">
+        <v>-67000</v>
+      </c>
+      <c r="X32" s="3">
+        <v>-109000</v>
+      </c>
+      <c r="Y32" s="3">
         <v>25000</v>
       </c>
-      <c r="L32" s="3">
-        <v>-124000</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-18000</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-111000</v>
-      </c>
-      <c r="O32" s="3">
-        <v>89000</v>
-      </c>
-      <c r="P32" s="3">
-        <v>106000</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>94000</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-476000</v>
-      </c>
-      <c r="S32" s="3">
-        <v>171000</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-69000</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-99000</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-67000</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-109000</v>
-      </c>
-      <c r="X32" s="3">
-        <v>25000</v>
-      </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-252000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-148000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1580000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-453000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-494000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>135000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-9986000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-966000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-400000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-417000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1240000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1069000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2101000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2308000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3418000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>407000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>48000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>120000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>515000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>106000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>205000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>223000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2534,155 +2609,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-252000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-148000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1580000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-453000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-494000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>135000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-9986000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-966000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-400000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-417000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1240000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1069000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2101000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2308000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3418000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>407000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>48000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>120000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>515000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>106000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>205000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>223000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2708,8 +2792,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2735,118 +2820,122 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4566000</v>
+      </c>
+      <c r="E41" s="3">
         <v>4294000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4888000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3868000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5312000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3336000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3613000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2976000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3780000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2383000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3027000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2594000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3731000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2422000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2575000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4162000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3905000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3116000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2834000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2008000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2091000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1893000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1683000</v>
       </c>
     </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E42" s="3">
         <v>32000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>29000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>36000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>17000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>18000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>68000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>93000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>24000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>83000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>72000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>40000</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -2877,79 +2966,85 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4136000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3316000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3210000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2818000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3887000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3498000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3599000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3643000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4532000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3683000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3485000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3558000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6380000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6669000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>7049000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2426000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2446000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2462000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2657000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2476000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2537000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2444000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2473000</v>
       </c>
     </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2986,8 +3081,8 @@
       <c r="N44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3019,363 +3114,381 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4483000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1876000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2251000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1909000</v>
       </c>
-      <c r="G45" s="3">
-        <v>2129000</v>
-      </c>
       <c r="H45" s="3">
+        <v>4758000</v>
+      </c>
+      <c r="I45" s="3">
         <v>2140000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2659000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2742000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2906000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2755000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3607000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3374000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3888000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3581000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5825000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>585000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>913000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1078000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1237000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1381000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1502000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1141000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>561000</v>
       </c>
     </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13206000</v>
+      </c>
+      <c r="E46" s="3">
         <v>13062000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>13611000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12782000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>14078000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12505000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>13430000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>13902000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>14218000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12831000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>13773000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>13727000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>13999000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>12672000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>15449000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>7173000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>7264000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6656000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6728000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5865000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6130000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5478000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4717000</v>
       </c>
     </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1250000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1276000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1262000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1293000</v>
       </c>
-      <c r="G47" s="3">
-        <v>1098000</v>
-      </c>
       <c r="H47" s="3">
-        <v>1257000</v>
+        <v>1331000</v>
       </c>
       <c r="I47" s="3">
+        <v>1474000</v>
+      </c>
+      <c r="J47" s="3">
         <v>1517000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1437000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1470000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1443000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1491000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1499000</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
-      <c r="R47" s="3" t="s">
+      <c r="Q47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S47" s="3">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T47" s="3">
         <v>543000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>545000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>559000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>522000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>507000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>536000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>530000</v>
       </c>
     </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8082000</v>
+      </c>
+      <c r="E48" s="3">
         <v>6517000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6413000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6211000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7214000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6158000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6043000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5937000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7730000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5810000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5473000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5325000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8490000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8365000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8515000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1328000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1336000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1310000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1239000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1189000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1206000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1125000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1088000</v>
       </c>
     </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>74163000</v>
+      </c>
+      <c r="E49" s="3">
         <v>73813000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>74662000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>75600000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>78314000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>79675000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>80907000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>91978000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>95784000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>97055000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>100888000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>103370000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>106072000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>109482000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>113117000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>22611000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>23061000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>23429000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>23694000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>23765000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>24149000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>24194000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>24618000</v>
       </c>
     </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3445,8 +3558,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3516,79 +3632,85 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2762000</v>
+      </c>
+      <c r="E52" s="3">
         <v>5851000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5779000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5793000</v>
       </c>
-      <c r="G52" s="3">
-        <v>3243000</v>
-      </c>
       <c r="H52" s="3">
-        <v>6738000</v>
+        <v>3010000</v>
       </c>
       <c r="I52" s="3">
+        <v>6521000</v>
+      </c>
+      <c r="J52" s="3">
         <v>6132000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6565000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2858000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6610000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6993000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6663000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5440000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5530000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5159000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2687000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2223000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2378000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2352000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2284000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2095000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2105000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2136000</v>
       </c>
     </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3658,79 +3780,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>100085000</v>
+      </c>
+      <c r="E54" s="3">
         <v>100519000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>101727000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>101679000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>104560000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>106333000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>108029000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>119819000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>122757000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>123749000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>128618000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>130584000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>134001000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>136049000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>142240000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>33799000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>34427000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>34318000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>34572000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>33625000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>34087000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>33438000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>33089000</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3756,8 +3884,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3783,434 +3912,453 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1093000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1083000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1074000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1008000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1055000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1120000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1151000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1245000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1260000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1329000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1689000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1123000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1454000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1534000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1397000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>521000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>412000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2361000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2174000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2128000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>397000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>403000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>367000</v>
       </c>
     </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>573000</v>
+      </c>
+      <c r="E58" s="3">
         <v>139000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>221000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2779000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3162000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3043000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3669000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3430000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2186000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1302000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3001000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3496000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>447000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1338000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1175000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>794000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>397000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>349000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>585000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>351000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>392000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>336000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>339000</v>
       </c>
     </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2310000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1649000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1527000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1600000</v>
       </c>
-      <c r="G59" s="3">
-        <v>1569000</v>
-      </c>
       <c r="H59" s="3">
+        <v>2213000</v>
+      </c>
+      <c r="I59" s="3">
         <v>1788000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2022000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2312000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1924000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2431000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2020000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2099000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>13116000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11804000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11864000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2247000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2650000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>625000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>806000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>663000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2293000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2017000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1870000</v>
       </c>
     </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12500000</v>
+      </c>
+      <c r="E60" s="3">
         <v>12163000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>13040000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>15286000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>15810000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>15695000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>17768000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>16956000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>15332000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>14588000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>16906000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>16380000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>15017000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>14676000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>14436000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3562000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3459000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3335000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3565000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3142000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3082000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2756000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2576000</v>
       </c>
     </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>36188000</v>
+      </c>
+      <c r="E61" s="3">
         <v>33382000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>34411000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>34647000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>39844000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>37166000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>37293000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>39155000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>45104000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>43504000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>44289000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>45435000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>48820000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>48799000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>51594000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>13605000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>14617000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>14436000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>14462000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>14675000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>15253000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>14981000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>14944000</v>
       </c>
     </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7263000</v>
+      </c>
+      <c r="E62" s="3">
         <v>10734000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>10205000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9651000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6529000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9769000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>9532000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9892000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6689000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>10275000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>10527000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>10337000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>21497000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>22494000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>23263000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3070000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2955000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3149000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3237000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3233000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3369000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3661000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3769000</v>
       </c>
     </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4280,8 +4428,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4351,8 +4502,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4422,79 +4576,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>62919000</v>
+      </c>
+      <c r="E66" s="3">
         <v>63214000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>64381000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>66508000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>69622000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>70159000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>72614000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>74525000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>76285000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>77607000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>81833000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>82742000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>86906000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>87532000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>90857000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>21830000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>22828000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>22707000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>23034000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>22810000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>23623000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>23351000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>23222000</v>
       </c>
     </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4520,8 +4680,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4591,8 +4752,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4662,8 +4826,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4733,8 +4900,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4804,79 +4974,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-11512000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-11260000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-11112000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-12692000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-12239000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-11745000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-11880000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1894000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-928000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-526000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-105000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1133000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2205000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>4306000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>6614000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>10033000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>9580000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>9522000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>9360000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>8682000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>8543000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>8278000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>7980000</v>
       </c>
     </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4946,8 +5122,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5017,8 +5196,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5088,79 +5270,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>35919000</v>
+      </c>
+      <c r="E76" s="3">
         <v>36018000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>36049000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>33836000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>34037000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>35100000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>34345000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>44151000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>45226000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>44774000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>45452000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>46496000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>47095000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>48517000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>51383000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>11969000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>11599000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>11611000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>11538000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>10815000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>10464000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>10087000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>9867000</v>
       </c>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5230,155 +5418,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-252000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-148000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1580000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-453000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-494000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>135000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-9986000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-966000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-400000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-417000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1240000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1069000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2101000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2308000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3418000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>407000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>48000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>120000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>515000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>106000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>205000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>223000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5404,79 +5601,83 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1643000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1762000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1744000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1888000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2024000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1989000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1914000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2058000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2169000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2233000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2266000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>525000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>6253000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>6174000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>7382000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1494000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1305000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1560000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1114000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1104000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1196000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1104000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>985000</v>
       </c>
     </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5546,8 +5747,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5617,8 +5821,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5688,8 +5895,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5759,8 +5969,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5830,79 +6043,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1804000</v>
+      </c>
+      <c r="E89" s="3">
         <v>979000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>983000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>553000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2715000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>847000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1228000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>585000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3578000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2516000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2014000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-631000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2846000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>124000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1011000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>323000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>884000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>811000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>834000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>269000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>553000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>860000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>991000</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5928,79 +6147,83 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-421000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-278000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-281000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-251000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-286000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-215000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-252000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-195000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-268000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-457000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-292000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-299000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-364000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-316000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-222000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-85000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-100000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-106000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-77000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-90000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-112000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-73000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-112000</v>
       </c>
     </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6070,8 +6293,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6141,79 +6367,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-418000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-330000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-236000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-195000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>6000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-218000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>70000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-207000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-234000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-458000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-310000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-257000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-218000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>862000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>2351000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>529000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-26000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-226000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>40000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>156000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-153000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-396000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-84000</v>
       </c>
     </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6239,8 +6471,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6277,8 +6510,8 @@
       <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -6310,8 +6543,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6381,8 +6617,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6452,8 +6691,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6523,217 +6765,229 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1117000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1237000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>9000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1895000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-600000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-875000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1037000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1237000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1529000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2625000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1251000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-432000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1272000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2313000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3570000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-587000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-42000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-273000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-69000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-469000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-277000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-274000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-739000</v>
       </c>
     </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-195000</v>
+      </c>
+      <c r="E101" s="3">
         <v>119000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-30000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-74000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>74000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-80000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-15000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>29000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>61000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-56000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-61000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-5000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>61000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-56000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-61000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-5000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-37000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-20000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>21000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-70000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>43000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>28000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>272000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-593000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>917000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1442000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1926000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-127000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>231000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-933000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1889000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-647000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>438000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1291000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1417000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1383000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-269000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>260000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>779000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>292000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>826000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-114000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>166000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>218000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>204000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WBD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WBD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
   <si>
     <t>WBD</t>
   </si>
@@ -656,329 +656,342 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="19" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8893000</v>
+      </c>
+      <c r="E8" s="3">
         <v>9460000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9045000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9812000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8979000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>10027000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9623000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9713000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9958000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>10284000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9979000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10358000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>10700000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>11008000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>9823000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>9827000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3159000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3187000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3150000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3062000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2792000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2886000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2561000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2541000</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4601000</v>
+      </c>
+      <c r="E9" s="3">
         <v>5119000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4528000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5967000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5096000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5457000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5036000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6204000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6058000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6000000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5118000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6636000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6589000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6954000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4718000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>6123000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1232000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1065000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1527000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1054000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>969000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1089000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1002000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>804000</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4292000</v>
+      </c>
+      <c r="E10" s="3">
         <v>4341000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4517000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3845000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3883000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4570000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4587000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3509000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3900000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4284000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4861000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3722000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4111000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4054000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5105000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3704000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1927000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2122000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1623000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2008000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1823000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1797000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1559000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1737000</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1005,8 +1018,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1079,8 +1093,11 @@
       <c r="Z12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1153,156 +1170,165 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>3260000</v>
+      </c>
+      <c r="E14" s="3">
         <v>355000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>178000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-2835000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>263000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>489000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>174000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>8832000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>118000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>8000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>495000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>215000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>308000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1198000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2430000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1535000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>9000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>5000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>15000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>8000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>18000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>150000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>70000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>122000</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1226000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1315000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1375000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1447000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1547000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1643000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1762000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1744000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1888000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2024000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1989000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1914000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2058000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2169000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2233000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>2266000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>525000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>539000</v>
-      </c>
-      <c r="U15" s="3">
-        <v>341000</v>
       </c>
       <c r="V15" s="3">
         <v>341000</v>
       </c>
       <c r="W15" s="3">
+        <v>341000</v>
+      </c>
+      <c r="X15" s="3">
         <v>361000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>358000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>341000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>334000</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1326,156 +1352,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8129000</v>
+      </c>
+      <c r="E17" s="3">
         <v>8762000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8255000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9871000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8758000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9385000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9121000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>10365000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10118000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10425000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9385000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11127000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>10988000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>12902000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>12013000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>13466000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2806000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2679000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2827000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2284000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2399000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2406000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2046000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1895000</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>764000</v>
+      </c>
+      <c r="E18" s="3">
         <v>698000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>790000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-59000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>221000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>642000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>502000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-652000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-160000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-141000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>594000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-769000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-288000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1894000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2190000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-3639000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>353000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>508000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>323000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>778000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>393000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>480000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>515000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>646000</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1502,378 +1535,394 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>62000</v>
+      </c>
+      <c r="E20" s="3">
         <v>200000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>62000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-88000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-14000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>135000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>26000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>92000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>103000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-25000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>124000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>18000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>111000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-89000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-106000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-94000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>476000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-171000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>69000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>99000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>67000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>109000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-25000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1928000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1813000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2103000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1476000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1782000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2150000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2238000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1000000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1625000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1908000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2459000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1127000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1659000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4270000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3878000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3649000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2323000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1642000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1952000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1991000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1564000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1785000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1594000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1613000</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>584000</v>
+      </c>
+      <c r="E22" s="3">
         <v>587000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>570000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>469000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>470000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>412000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>529000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>522000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>498000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>540000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>550000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>518000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>576000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>558000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>555000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>511000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>153000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>154000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>159000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>157000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>163000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>173000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>171000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>172000</v>
       </c>
     </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3120000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-408000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>27000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2454000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-434000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-356000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-178000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-10035000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-819000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-613000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-532000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1480000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1238000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2541000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2851000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4244000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>676000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>183000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>233000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>720000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>297000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>416000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>319000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>456000</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-214000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-161000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>170000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>866000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>15000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>284000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-319000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-7000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>136000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-221000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-125000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-260000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-178000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-462000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-566000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-836000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>201000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>92000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>36000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>106000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>98000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>156000</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1946,156 +1995,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2906000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-247000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-143000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1588000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-449000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-640000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>141000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-10028000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-955000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-392000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-407000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1220000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1060000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2079000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2285000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3408000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>475000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>91000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>197000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>718000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>191000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>318000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>330000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>300000</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2916000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-251000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-148000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1580000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-453000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-493000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>135000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-9986000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-970000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-400000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-417000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1240000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1069000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2101000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2308000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3418000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>407000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>48000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>120000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>515000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>106000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>205000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>223000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2168,8 +2226,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2242,8 +2303,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2316,8 +2380,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2390,156 +2457,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-62000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-200000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-62000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>88000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>14000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-135000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-26000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-92000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-103000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>25000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-124000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-18000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-111000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>89000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>106000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>94000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-476000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>171000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-69000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-99000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-67000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-109000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>25000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2916000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-252000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-148000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1580000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-453000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-494000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>135000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-9986000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-966000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-400000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-417000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1240000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1069000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2101000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2308000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3418000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>407000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>48000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>120000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>515000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>106000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>205000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>223000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2612,161 +2688,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2916000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-252000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-148000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1580000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-453000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-494000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>135000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-9986000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-966000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-400000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-417000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1240000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1069000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2101000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2308000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3418000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>407000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>48000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>120000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>515000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>106000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>205000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>223000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2793,8 +2878,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2821,124 +2907,128 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3264000</v>
+      </c>
+      <c r="E41" s="3">
         <v>4566000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4294000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4888000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3868000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5312000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3336000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3613000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2976000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3780000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2383000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3027000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2594000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3731000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2422000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2575000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4162000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3905000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3116000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2834000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2008000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2091000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1893000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1683000</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E42" s="3">
         <v>17000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>32000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>29000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>36000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>17000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>18000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>68000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>93000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>24000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>83000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>72000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>40000</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -2969,82 +3059,88 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3357000</v>
+      </c>
+      <c r="E43" s="3">
         <v>4136000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3316000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3210000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2818000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3887000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3498000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3599000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3643000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4532000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3683000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3485000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3558000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6380000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6669000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7049000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2426000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2446000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2462000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2657000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2476000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2537000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2444000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2473000</v>
       </c>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3084,8 +3180,8 @@
       <c r="O44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3117,378 +3213,396 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1724000</v>
+      </c>
+      <c r="E45" s="3">
         <v>4483000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1876000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2251000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1909000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4758000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2140000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2659000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2742000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2906000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2755000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3607000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3374000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3888000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3581000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5825000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>585000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>913000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1078000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1237000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1381000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1502000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1141000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>561000</v>
       </c>
     </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>11741000</v>
+      </c>
+      <c r="E46" s="3">
         <v>13206000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>13062000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>13611000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>12782000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>14078000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12505000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>13430000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>13902000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>14218000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12831000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>13773000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>13727000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>13999000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>12672000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>15449000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>7173000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>7264000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6656000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6728000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5865000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6130000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>5478000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4717000</v>
       </c>
     </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1232000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1250000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1276000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1262000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1293000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1331000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1474000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1517000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1437000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1470000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1443000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1491000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1499000</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
-      </c>
-      <c r="S47" s="3" t="s">
+      <c r="R47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T47" s="3">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U47" s="3">
         <v>543000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>545000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>559000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>522000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>507000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>536000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>530000</v>
       </c>
     </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6642000</v>
+      </c>
+      <c r="E48" s="3">
         <v>8082000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6517000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6413000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6211000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7214000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6158000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6043000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5937000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7730000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5810000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5473000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5325000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8490000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8365000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8515000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1328000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1336000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1310000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1239000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1189000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1206000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1125000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1088000</v>
       </c>
     </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>71989000</v>
+      </c>
+      <c r="E49" s="3">
         <v>74163000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>73813000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>74662000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>75600000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>78314000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>79675000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>80907000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>91978000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>95784000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>97055000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>100888000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>103370000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>106072000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>109482000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>113117000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>22611000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>23061000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>23429000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>23694000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>23765000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>24149000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>24194000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>24618000</v>
       </c>
     </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3561,8 +3675,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3635,82 +3752,88 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6233000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2762000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5851000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5779000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5793000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3010000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6521000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6132000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6565000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2858000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6610000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6993000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6663000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5440000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5530000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5159000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2687000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2223000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2378000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2352000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2284000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2095000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2105000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2136000</v>
       </c>
     </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3783,82 +3906,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>97837000</v>
+      </c>
+      <c r="E54" s="3">
         <v>100085000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>100519000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>101727000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>101679000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>104560000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>106333000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>108029000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>119819000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>122757000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>123749000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>128618000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>130584000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>134001000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>136049000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>142240000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>33799000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>34427000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>34318000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>34572000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>33625000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>34087000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>33438000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>33089000</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3885,8 +4014,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3913,452 +4043,471 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1110000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1093000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1083000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1074000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1008000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1055000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1120000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1151000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1245000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1260000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1329000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1689000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1123000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1454000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1534000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1397000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>521000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>412000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2361000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2174000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2128000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>397000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>403000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>367000</v>
       </c>
     </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1493000</v>
+      </c>
+      <c r="E58" s="3">
         <v>573000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>139000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>221000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2779000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3162000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3043000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3669000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3430000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2186000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1302000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3001000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3496000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>447000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1338000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1175000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>794000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>397000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>349000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>585000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>351000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>392000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>336000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>339000</v>
       </c>
     </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1592000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2310000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1649000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1527000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1600000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2213000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1788000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2022000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2312000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1924000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2431000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2020000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2099000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>13116000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11804000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11864000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2247000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2650000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>625000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>806000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>663000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2293000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2017000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1870000</v>
       </c>
     </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>16115000</v>
+      </c>
+      <c r="E60" s="3">
         <v>12500000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12163000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>13040000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>15286000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>15810000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>15695000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>17768000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>16956000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>15332000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>14588000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>16906000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>16380000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>15017000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>14676000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>14436000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3562000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3459000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3335000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3565000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3142000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3082000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2756000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2576000</v>
       </c>
     </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>30973000</v>
+      </c>
+      <c r="E61" s="3">
         <v>36188000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>33382000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>34411000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>34647000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>39844000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>37166000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>37293000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>39155000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>45104000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>43504000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>44289000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>45435000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>48820000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>48799000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>51594000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>13605000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>14617000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>14436000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>14462000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>14675000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>15253000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>14981000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>14944000</v>
       </c>
     </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10809000</v>
+      </c>
+      <c r="E62" s="3">
         <v>7263000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>10734000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>10205000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>9651000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6529000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>9769000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9532000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>9892000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6689000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>10275000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>10527000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>10337000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>21497000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>22494000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>23263000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3070000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2955000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3149000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3237000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3233000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3369000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3661000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3769000</v>
       </c>
     </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4431,8 +4580,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4505,8 +4657,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4579,82 +4734,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>64130000</v>
+      </c>
+      <c r="E66" s="3">
         <v>62919000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>63214000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>64381000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>66508000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>69622000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>70159000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>72614000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>74525000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>76285000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>77607000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>81833000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>82742000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>86906000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>87532000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>90857000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>21830000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>22828000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>22707000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>23034000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>22810000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>23623000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>23351000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>23222000</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4681,8 +4842,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4755,8 +4917,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4829,8 +4994,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4903,8 +5071,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4977,82 +5148,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-14428000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-11512000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-11260000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-11112000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-12692000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-12239000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-11745000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-11880000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1894000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-928000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-526000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-105000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1133000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2205000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>4306000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>6614000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>10033000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>9580000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>9522000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>9360000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>8682000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>8543000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>8278000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>7980000</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5125,8 +5302,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5199,8 +5379,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5273,82 +5456,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>32578000</v>
+      </c>
+      <c r="E76" s="3">
         <v>35919000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>36018000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>36049000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>33836000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>34037000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>35100000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>34345000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>44151000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>45226000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>44774000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>45452000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>46496000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>47095000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>48517000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>51383000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>11969000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>11599000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>11611000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>11538000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>10815000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>10464000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>10087000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>9867000</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5421,161 +5610,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2916000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-252000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-148000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1580000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-453000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-494000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>135000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-9986000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-966000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-400000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-417000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1240000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1069000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2101000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2308000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3418000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>407000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>48000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>120000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>515000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>106000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>205000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>223000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5602,82 +5800,86 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1547000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1643000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1762000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1744000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1888000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2024000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1989000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1914000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2058000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2169000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2233000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2266000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>525000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>6253000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>6174000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>7382000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1494000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1305000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1560000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1114000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1104000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1196000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1104000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>985000</v>
       </c>
     </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5750,8 +5952,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5824,8 +6029,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5898,8 +6106,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5972,8 +6183,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6046,82 +6260,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-208000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1804000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>979000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>983000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>553000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2715000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>847000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1228000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>585000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3578000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2516000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2014000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-631000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2846000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>124000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1011000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>323000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>884000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>811000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>834000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>269000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>553000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>860000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>991000</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6148,82 +6368,86 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-268000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-421000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-278000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-281000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-251000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-286000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-215000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-252000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-195000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-268000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-457000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-292000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-299000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-364000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-316000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-222000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-85000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-100000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-106000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-77000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-90000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-112000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-73000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-112000</v>
       </c>
     </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6296,8 +6520,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6370,82 +6597,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-282000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-418000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-330000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-236000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-195000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>6000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-218000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>70000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-207000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-234000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-458000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-310000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-257000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-218000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>862000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>2351000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>529000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-26000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-226000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>40000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>156000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-153000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-396000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-84000</v>
       </c>
     </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6472,8 +6705,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6513,8 +6747,8 @@
       <c r="O96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -6546,8 +6780,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6620,8 +6857,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6694,8 +6934,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6768,226 +7011,238 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-756000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1117000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1237000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>9000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1895000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-600000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-875000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1037000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1237000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1529000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2625000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1251000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-432000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1272000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2313000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-3570000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-587000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-42000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-273000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-69000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-469000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-277000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-274000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-739000</v>
       </c>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>95000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-195000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>119000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-30000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-74000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>74000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-80000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-15000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>29000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>61000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-56000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-61000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-5000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>61000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-56000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-61000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-5000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-37000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-20000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>21000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-70000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>43000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>28000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1302000</v>
+      </c>
+      <c r="E102" s="3">
         <v>272000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-593000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>917000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1442000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1926000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-127000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>231000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-933000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1889000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-647000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>438000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1291000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1417000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1383000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-269000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>260000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>779000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>292000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>826000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-114000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>166000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>218000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>204000</v>
       </c>
     </row>
